--- a/fiis_b3.xlsx
+++ b/fiis_b3.xlsx
@@ -611,11 +611,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -700,11 +696,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -789,11 +781,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -878,11 +866,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -967,11 +951,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -1056,11 +1036,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -1145,11 +1121,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -1234,11 +1206,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -1323,11 +1291,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -1412,11 +1376,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -1501,11 +1461,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -1590,11 +1546,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -1679,11 +1631,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -1768,11 +1716,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -1857,11 +1801,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -1946,11 +1886,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -2035,11 +1971,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -2124,11 +2056,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -2213,11 +2141,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -2302,11 +2226,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -2391,11 +2311,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -2480,11 +2396,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -2569,11 +2481,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -2658,11 +2566,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -2747,11 +2651,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -2836,11 +2736,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -2925,11 +2821,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -3014,11 +2906,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -3103,11 +2991,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -3192,11 +3076,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -3281,11 +3161,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -3370,11 +3246,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -3459,11 +3331,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -3548,11 +3416,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -3637,11 +3501,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -3726,11 +3586,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -3815,11 +3671,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -3904,11 +3756,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -3993,11 +3841,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -4082,11 +3926,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -4171,11 +4011,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -4260,11 +4096,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -4349,11 +4181,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -4438,11 +4266,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -4527,11 +4351,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -4616,11 +4436,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -4705,11 +4521,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -4794,11 +4606,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -4883,11 +4691,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -4972,11 +4776,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -5061,11 +4861,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -5150,11 +4946,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -5239,11 +5031,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -5328,11 +5116,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -5417,11 +5201,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -5506,11 +5286,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -5595,11 +5371,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V58" t="inlineStr"/>
       <c r="W58" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -5684,11 +5456,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V59" t="inlineStr"/>
       <c r="W59" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -5773,11 +5541,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -5862,11 +5626,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V61" t="inlineStr"/>
       <c r="W61" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -5951,11 +5711,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V62" t="inlineStr"/>
       <c r="W62" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -6040,11 +5796,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V63" t="inlineStr"/>
       <c r="W63" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -6129,11 +5881,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V64" t="inlineStr"/>
       <c r="W64" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -6218,11 +5966,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V65" t="inlineStr"/>
       <c r="W65" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -6307,11 +6051,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V66" t="inlineStr"/>
       <c r="W66" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -6396,11 +6136,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V67" t="inlineStr"/>
       <c r="W67" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -6485,11 +6221,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V68" t="inlineStr"/>
       <c r="W68" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -6574,11 +6306,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V69" t="inlineStr"/>
       <c r="W69" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -6663,11 +6391,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V70" t="inlineStr"/>
       <c r="W70" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -6752,11 +6476,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V71" t="inlineStr"/>
       <c r="W71" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -6841,11 +6561,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V72" t="inlineStr"/>
       <c r="W72" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -6930,11 +6646,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V73" t="inlineStr"/>
       <c r="W73" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -7019,11 +6731,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V74" t="inlineStr"/>
       <c r="W74" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -7108,11 +6816,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V75" t="inlineStr"/>
       <c r="W75" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -7197,11 +6901,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V76" t="inlineStr"/>
       <c r="W76" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -7286,11 +6986,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V77" t="inlineStr"/>
       <c r="W77" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -7375,11 +7071,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V78" t="inlineStr"/>
       <c r="W78" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -7464,11 +7156,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V79" t="inlineStr"/>
       <c r="W79" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -7553,11 +7241,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V80" t="inlineStr"/>
       <c r="W80" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -7642,11 +7326,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V81" t="inlineStr"/>
       <c r="W81" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -7731,11 +7411,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V82" t="inlineStr"/>
       <c r="W82" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -7820,11 +7496,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V83" t="inlineStr"/>
       <c r="W83" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -7909,11 +7581,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V84" t="inlineStr"/>
       <c r="W84" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -7998,11 +7666,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V85" t="inlineStr"/>
       <c r="W85" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -8087,11 +7751,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V86" t="inlineStr"/>
       <c r="W86" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -8176,11 +7836,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V87" t="inlineStr"/>
       <c r="W87" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -8265,11 +7921,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V88" t="inlineStr"/>
       <c r="W88" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -8354,11 +8006,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V89" t="inlineStr"/>
       <c r="W89" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -8443,11 +8091,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V90" t="inlineStr"/>
       <c r="W90" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -8532,11 +8176,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V91" t="inlineStr"/>
       <c r="W91" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -8621,11 +8261,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V92" t="inlineStr"/>
       <c r="W92" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -8710,11 +8346,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V93" t="inlineStr"/>
       <c r="W93" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -8799,11 +8431,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V94" t="inlineStr"/>
       <c r="W94" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -8888,11 +8516,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V95" t="inlineStr"/>
       <c r="W95" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -8977,11 +8601,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V96" t="inlineStr"/>
       <c r="W96" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -9066,11 +8686,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V97" t="inlineStr"/>
       <c r="W97" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -9155,11 +8771,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V98" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V98" t="inlineStr"/>
       <c r="W98" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -9244,11 +8856,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V99" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V99" t="inlineStr"/>
       <c r="W99" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -9333,11 +8941,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V100" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V100" t="inlineStr"/>
       <c r="W100" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -9422,11 +9026,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V101" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V101" t="inlineStr"/>
       <c r="W101" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -9511,11 +9111,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V102" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V102" t="inlineStr"/>
       <c r="W102" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -9600,11 +9196,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V103" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V103" t="inlineStr"/>
       <c r="W103" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -9689,11 +9281,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V104" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V104" t="inlineStr"/>
       <c r="W104" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -9778,11 +9366,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V105" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V105" t="inlineStr"/>
       <c r="W105" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -9867,11 +9451,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V106" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V106" t="inlineStr"/>
       <c r="W106" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -9956,11 +9536,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V107" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V107" t="inlineStr"/>
       <c r="W107" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -10045,11 +9621,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V108" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V108" t="inlineStr"/>
       <c r="W108" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -10134,11 +9706,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V109" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V109" t="inlineStr"/>
       <c r="W109" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -10223,11 +9791,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V110" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V110" t="inlineStr"/>
       <c r="W110" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -10312,11 +9876,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V111" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V111" t="inlineStr"/>
       <c r="W111" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -10401,11 +9961,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V112" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V112" t="inlineStr"/>
       <c r="W112" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -10490,11 +10046,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V113" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V113" t="inlineStr"/>
       <c r="W113" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -10579,11 +10131,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V114" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V114" t="inlineStr"/>
       <c r="W114" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -10668,11 +10216,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V115" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V115" t="inlineStr"/>
       <c r="W115" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -10757,11 +10301,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V116" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V116" t="inlineStr"/>
       <c r="W116" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -10846,11 +10386,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V117" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V117" t="inlineStr"/>
       <c r="W117" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -10935,11 +10471,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V118" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V118" t="inlineStr"/>
       <c r="W118" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -11024,11 +10556,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V119" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V119" t="inlineStr"/>
       <c r="W119" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -11113,11 +10641,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V120" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V120" t="inlineStr"/>
       <c r="W120" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -11202,11 +10726,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V121" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V121" t="inlineStr"/>
       <c r="W121" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -11291,11 +10811,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V122" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V122" t="inlineStr"/>
       <c r="W122" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -11380,11 +10896,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V123" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V123" t="inlineStr"/>
       <c r="W123" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -11469,11 +10981,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V124" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V124" t="inlineStr"/>
       <c r="W124" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -11558,11 +11066,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V125" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V125" t="inlineStr"/>
       <c r="W125" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -11647,11 +11151,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V126" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V126" t="inlineStr"/>
       <c r="W126" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -11736,11 +11236,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V127" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V127" t="inlineStr"/>
       <c r="W127" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -11825,11 +11321,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V128" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V128" t="inlineStr"/>
       <c r="W128" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -11914,11 +11406,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V129" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V129" t="inlineStr"/>
       <c r="W129" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -12003,11 +11491,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V130" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V130" t="inlineStr"/>
       <c r="W130" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -12092,11 +11576,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V131" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V131" t="inlineStr"/>
       <c r="W131" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -12181,11 +11661,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V132" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V132" t="inlineStr"/>
       <c r="W132" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -12270,11 +11746,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V133" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V133" t="inlineStr"/>
       <c r="W133" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -12359,11 +11831,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V134" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V134" t="inlineStr"/>
       <c r="W134" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -12448,11 +11916,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V135" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V135" t="inlineStr"/>
       <c r="W135" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -12537,11 +12001,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V136" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V136" t="inlineStr"/>
       <c r="W136" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -12626,11 +12086,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V137" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V137" t="inlineStr"/>
       <c r="W137" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -12715,11 +12171,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V138" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V138" t="inlineStr"/>
       <c r="W138" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -12804,11 +12256,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V139" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V139" t="inlineStr"/>
       <c r="W139" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -12893,11 +12341,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V140" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V140" t="inlineStr"/>
       <c r="W140" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -12982,11 +12426,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V141" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V141" t="inlineStr"/>
       <c r="W141" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -13071,11 +12511,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V142" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V142" t="inlineStr"/>
       <c r="W142" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -13160,11 +12596,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V143" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V143" t="inlineStr"/>
       <c r="W143" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -13249,11 +12681,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V144" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V144" t="inlineStr"/>
       <c r="W144" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -13338,11 +12766,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V145" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V145" t="inlineStr"/>
       <c r="W145" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -13427,11 +12851,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V146" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V146" t="inlineStr"/>
       <c r="W146" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -13516,11 +12936,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V147" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V147" t="inlineStr"/>
       <c r="W147" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -13605,11 +13021,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V148" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V148" t="inlineStr"/>
       <c r="W148" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -13694,11 +13106,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V149" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V149" t="inlineStr"/>
       <c r="W149" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -13783,11 +13191,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V150" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V150" t="inlineStr"/>
       <c r="W150" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -13872,11 +13276,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V151" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V151" t="inlineStr"/>
       <c r="W151" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -13961,11 +13361,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V152" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V152" t="inlineStr"/>
       <c r="W152" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -14050,11 +13446,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V153" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V153" t="inlineStr"/>
       <c r="W153" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -14139,11 +13531,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V154" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V154" t="inlineStr"/>
       <c r="W154" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -14228,11 +13616,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V155" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V155" t="inlineStr"/>
       <c r="W155" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -14317,11 +13701,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V156" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V156" t="inlineStr"/>
       <c r="W156" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -14406,11 +13786,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V157" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V157" t="inlineStr"/>
       <c r="W157" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -14495,11 +13871,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V158" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V158" t="inlineStr"/>
       <c r="W158" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -14584,11 +13956,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V159" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V159" t="inlineStr"/>
       <c r="W159" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -14673,11 +14041,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V160" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V160" t="inlineStr"/>
       <c r="W160" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -14762,11 +14126,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V161" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V161" t="inlineStr"/>
       <c r="W161" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -14851,11 +14211,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V162" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V162" t="inlineStr"/>
       <c r="W162" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -14940,11 +14296,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V163" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V163" t="inlineStr"/>
       <c r="W163" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -15029,11 +14381,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V164" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V164" t="inlineStr"/>
       <c r="W164" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -15118,11 +14466,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V165" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V165" t="inlineStr"/>
       <c r="W165" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -15207,11 +14551,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V166" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V166" t="inlineStr"/>
       <c r="W166" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -15296,11 +14636,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V167" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V167" t="inlineStr"/>
       <c r="W167" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -15385,11 +14721,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V168" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V168" t="inlineStr"/>
       <c r="W168" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -15474,11 +14806,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V169" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V169" t="inlineStr"/>
       <c r="W169" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -15563,11 +14891,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V170" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V170" t="inlineStr"/>
       <c r="W170" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -15652,11 +14976,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V171" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V171" t="inlineStr"/>
       <c r="W171" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -15741,11 +15061,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V172" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V172" t="inlineStr"/>
       <c r="W172" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -15830,11 +15146,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V173" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V173" t="inlineStr"/>
       <c r="W173" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -15919,11 +15231,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V174" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V174" t="inlineStr"/>
       <c r="W174" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -16008,11 +15316,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V175" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V175" t="inlineStr"/>
       <c r="W175" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -16097,11 +15401,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V176" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V176" t="inlineStr"/>
       <c r="W176" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -16186,11 +15486,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V177" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V177" t="inlineStr"/>
       <c r="W177" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -16275,11 +15571,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V178" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V178" t="inlineStr"/>
       <c r="W178" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -16364,11 +15656,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V179" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V179" t="inlineStr"/>
       <c r="W179" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -16453,11 +15741,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V180" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V180" t="inlineStr"/>
       <c r="W180" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -16542,11 +15826,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V181" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V181" t="inlineStr"/>
       <c r="W181" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -16631,11 +15911,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V182" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V182" t="inlineStr"/>
       <c r="W182" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -16720,11 +15996,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V183" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V183" t="inlineStr"/>
       <c r="W183" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -16809,11 +16081,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V184" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V184" t="inlineStr"/>
       <c r="W184" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -16898,11 +16166,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V185" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V185" t="inlineStr"/>
       <c r="W185" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -16987,11 +16251,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V186" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V186" t="inlineStr"/>
       <c r="W186" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -17076,11 +16336,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V187" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V187" t="inlineStr"/>
       <c r="W187" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -17165,11 +16421,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V188" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V188" t="inlineStr"/>
       <c r="W188" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -17254,11 +16506,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V189" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V189" t="inlineStr"/>
       <c r="W189" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -17343,11 +16591,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V190" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V190" t="inlineStr"/>
       <c r="W190" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -17432,11 +16676,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V191" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V191" t="inlineStr"/>
       <c r="W191" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -17521,11 +16761,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V192" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V192" t="inlineStr"/>
       <c r="W192" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -17610,11 +16846,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V193" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V193" t="inlineStr"/>
       <c r="W193" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -17699,11 +16931,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V194" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V194" t="inlineStr"/>
       <c r="W194" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -17788,11 +17016,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V195" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V195" t="inlineStr"/>
       <c r="W195" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -17877,11 +17101,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V196" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V196" t="inlineStr"/>
       <c r="W196" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -17966,11 +17186,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V197" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V197" t="inlineStr"/>
       <c r="W197" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -18055,11 +17271,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V198" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V198" t="inlineStr"/>
       <c r="W198" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -18144,11 +17356,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V199" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V199" t="inlineStr"/>
       <c r="W199" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -18233,11 +17441,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V200" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V200" t="inlineStr"/>
       <c r="W200" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -18322,11 +17526,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V201" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V201" t="inlineStr"/>
       <c r="W201" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -18411,11 +17611,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V202" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V202" t="inlineStr"/>
       <c r="W202" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -18500,11 +17696,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V203" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V203" t="inlineStr"/>
       <c r="W203" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -18589,11 +17781,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V204" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V204" t="inlineStr"/>
       <c r="W204" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -18678,11 +17866,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V205" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V205" t="inlineStr"/>
       <c r="W205" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -18767,11 +17951,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V206" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V206" t="inlineStr"/>
       <c r="W206" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -18856,11 +18036,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V207" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V207" t="inlineStr"/>
       <c r="W207" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -18945,11 +18121,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V208" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V208" t="inlineStr"/>
       <c r="W208" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -19034,11 +18206,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V209" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V209" t="inlineStr"/>
       <c r="W209" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -19123,11 +18291,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V210" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V210" t="inlineStr"/>
       <c r="W210" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -19212,11 +18376,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V211" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V211" t="inlineStr"/>
       <c r="W211" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -19301,11 +18461,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V212" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V212" t="inlineStr"/>
       <c r="W212" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -19390,11 +18546,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V213" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V213" t="inlineStr"/>
       <c r="W213" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -19479,11 +18631,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V214" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V214" t="inlineStr"/>
       <c r="W214" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -19568,11 +18716,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V215" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V215" t="inlineStr"/>
       <c r="W215" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -19657,11 +18801,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V216" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V216" t="inlineStr"/>
       <c r="W216" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -19746,11 +18886,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V217" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V217" t="inlineStr"/>
       <c r="W217" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -19835,11 +18971,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V218" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V218" t="inlineStr"/>
       <c r="W218" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -19924,11 +19056,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V219" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V219" t="inlineStr"/>
       <c r="W219" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -20013,11 +19141,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V220" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V220" t="inlineStr"/>
       <c r="W220" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -20102,11 +19226,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V221" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V221" t="inlineStr"/>
       <c r="W221" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -20191,11 +19311,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V222" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V222" t="inlineStr"/>
       <c r="W222" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -20280,11 +19396,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V223" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V223" t="inlineStr"/>
       <c r="W223" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -20369,11 +19481,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V224" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V224" t="inlineStr"/>
       <c r="W224" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -20458,11 +19566,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V225" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V225" t="inlineStr"/>
       <c r="W225" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -20547,11 +19651,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V226" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V226" t="inlineStr"/>
       <c r="W226" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -20636,11 +19736,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V227" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V227" t="inlineStr"/>
       <c r="W227" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -20725,11 +19821,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V228" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V228" t="inlineStr"/>
       <c r="W228" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -20814,11 +19906,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V229" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V229" t="inlineStr"/>
       <c r="W229" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -20903,11 +19991,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V230" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V230" t="inlineStr"/>
       <c r="W230" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -20992,11 +20076,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V231" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V231" t="inlineStr"/>
       <c r="W231" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -21081,11 +20161,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V232" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V232" t="inlineStr"/>
       <c r="W232" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -21170,11 +20246,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V233" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V233" t="inlineStr"/>
       <c r="W233" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -21259,11 +20331,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V234" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V234" t="inlineStr"/>
       <c r="W234" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -21348,11 +20416,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V235" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V235" t="inlineStr"/>
       <c r="W235" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -21437,11 +20501,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V236" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V236" t="inlineStr"/>
       <c r="W236" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -21526,11 +20586,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V237" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V237" t="inlineStr"/>
       <c r="W237" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -21615,11 +20671,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V238" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V238" t="inlineStr"/>
       <c r="W238" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -21704,11 +20756,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V239" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V239" t="inlineStr"/>
       <c r="W239" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -21793,11 +20841,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V240" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V240" t="inlineStr"/>
       <c r="W240" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -21882,11 +20926,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V241" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V241" t="inlineStr"/>
       <c r="W241" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -21971,11 +21011,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V242" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V242" t="inlineStr"/>
       <c r="W242" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -22060,11 +21096,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V243" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V243" t="inlineStr"/>
       <c r="W243" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -22149,11 +21181,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V244" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V244" t="inlineStr"/>
       <c r="W244" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -22238,11 +21266,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V245" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V245" t="inlineStr"/>
       <c r="W245" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -22327,11 +21351,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V246" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V246" t="inlineStr"/>
       <c r="W246" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -22416,11 +21436,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V247" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V247" t="inlineStr"/>
       <c r="W247" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -22505,11 +21521,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V248" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V248" t="inlineStr"/>
       <c r="W248" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -22594,11 +21606,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V249" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V249" t="inlineStr"/>
       <c r="W249" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -22683,11 +21691,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V250" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V250" t="inlineStr"/>
       <c r="W250" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -22772,11 +21776,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V251" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V251" t="inlineStr"/>
       <c r="W251" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -22861,11 +21861,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V252" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V252" t="inlineStr"/>
       <c r="W252" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -22950,11 +21946,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V253" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V253" t="inlineStr"/>
       <c r="W253" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -23039,11 +22031,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V254" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V254" t="inlineStr"/>
       <c r="W254" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -23128,11 +22116,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V255" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V255" t="inlineStr"/>
       <c r="W255" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -23217,11 +22201,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V256" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V256" t="inlineStr"/>
       <c r="W256" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -23306,11 +22286,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V257" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V257" t="inlineStr"/>
       <c r="W257" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -23395,11 +22371,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V258" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V258" t="inlineStr"/>
       <c r="W258" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -23484,11 +22456,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V259" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V259" t="inlineStr"/>
       <c r="W259" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -23573,11 +22541,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V260" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V260" t="inlineStr"/>
       <c r="W260" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -23662,11 +22626,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V261" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V261" t="inlineStr"/>
       <c r="W261" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -23751,11 +22711,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V262" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V262" t="inlineStr"/>
       <c r="W262" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -23840,11 +22796,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V263" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V263" t="inlineStr"/>
       <c r="W263" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -23929,11 +22881,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V264" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V264" t="inlineStr"/>
       <c r="W264" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -24018,11 +22966,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V265" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V265" t="inlineStr"/>
       <c r="W265" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -24107,11 +23051,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V266" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V266" t="inlineStr"/>
       <c r="W266" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -24196,11 +23136,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V267" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V267" t="inlineStr"/>
       <c r="W267" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -24285,11 +23221,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V268" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V268" t="inlineStr"/>
       <c r="W268" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -24374,11 +23306,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V269" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V269" t="inlineStr"/>
       <c r="W269" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -24463,11 +23391,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V270" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V270" t="inlineStr"/>
       <c r="W270" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -24552,11 +23476,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V271" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V271" t="inlineStr"/>
       <c r="W271" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -24641,11 +23561,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V272" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V272" t="inlineStr"/>
       <c r="W272" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -24730,11 +23646,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V273" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V273" t="inlineStr"/>
       <c r="W273" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -24819,11 +23731,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V274" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V274" t="inlineStr"/>
       <c r="W274" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -24908,11 +23816,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V275" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V275" t="inlineStr"/>
       <c r="W275" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -24997,11 +23901,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V276" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V276" t="inlineStr"/>
       <c r="W276" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -25086,11 +23986,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V277" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V277" t="inlineStr"/>
       <c r="W277" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -25175,11 +24071,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V278" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V278" t="inlineStr"/>
       <c r="W278" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -25264,11 +24156,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V279" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V279" t="inlineStr"/>
       <c r="W279" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -25353,11 +24241,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V280" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V280" t="inlineStr"/>
       <c r="W280" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -25442,11 +24326,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V281" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V281" t="inlineStr"/>
       <c r="W281" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -25531,11 +24411,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V282" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V282" t="inlineStr"/>
       <c r="W282" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -25620,11 +24496,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V283" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V283" t="inlineStr"/>
       <c r="W283" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -25709,11 +24581,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V284" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V284" t="inlineStr"/>
       <c r="W284" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -25798,11 +24666,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V285" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V285" t="inlineStr"/>
       <c r="W285" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -25887,11 +24751,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V286" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V286" t="inlineStr"/>
       <c r="W286" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -25976,11 +24836,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V287" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V287" t="inlineStr"/>
       <c r="W287" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -26065,11 +24921,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V288" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V288" t="inlineStr"/>
       <c r="W288" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -26154,11 +25006,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V289" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V289" t="inlineStr"/>
       <c r="W289" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -26243,11 +25091,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V290" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V290" t="inlineStr"/>
       <c r="W290" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -26332,11 +25176,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V291" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V291" t="inlineStr"/>
       <c r="W291" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -26421,11 +25261,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V292" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V292" t="inlineStr"/>
       <c r="W292" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -26510,11 +25346,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V293" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V293" t="inlineStr"/>
       <c r="W293" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -26599,11 +25431,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V294" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V294" t="inlineStr"/>
       <c r="W294" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -26688,11 +25516,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V295" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V295" t="inlineStr"/>
       <c r="W295" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -26777,11 +25601,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V296" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V296" t="inlineStr"/>
       <c r="W296" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -26866,11 +25686,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V297" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V297" t="inlineStr"/>
       <c r="W297" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -26955,11 +25771,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V298" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V298" t="inlineStr"/>
       <c r="W298" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -27044,11 +25856,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V299" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V299" t="inlineStr"/>
       <c r="W299" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -27133,11 +25941,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V300" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V300" t="inlineStr"/>
       <c r="W300" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -27222,11 +26026,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V301" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V301" t="inlineStr"/>
       <c r="W301" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -27311,11 +26111,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V302" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V302" t="inlineStr"/>
       <c r="W302" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -27400,11 +26196,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V303" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V303" t="inlineStr"/>
       <c r="W303" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -27489,11 +26281,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V304" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V304" t="inlineStr"/>
       <c r="W304" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -27578,11 +26366,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V305" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V305" t="inlineStr"/>
       <c r="W305" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -27667,11 +26451,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V306" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V306" t="inlineStr"/>
       <c r="W306" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -27756,11 +26536,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V307" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V307" t="inlineStr"/>
       <c r="W307" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -27845,11 +26621,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V308" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V308" t="inlineStr"/>
       <c r="W308" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -27934,11 +26706,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V309" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V309" t="inlineStr"/>
       <c r="W309" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -28023,11 +26791,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V310" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V310" t="inlineStr"/>
       <c r="W310" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -28112,11 +26876,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V311" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V311" t="inlineStr"/>
       <c r="W311" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -28201,11 +26961,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V312" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V312" t="inlineStr"/>
       <c r="W312" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -28290,11 +27046,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V313" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V313" t="inlineStr"/>
       <c r="W313" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -28379,11 +27131,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V314" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V314" t="inlineStr"/>
       <c r="W314" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -28468,11 +27216,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V315" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V315" t="inlineStr"/>
       <c r="W315" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -28557,11 +27301,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V316" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V316" t="inlineStr"/>
       <c r="W316" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -28646,11 +27386,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V317" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V317" t="inlineStr"/>
       <c r="W317" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -28735,11 +27471,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V318" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V318" t="inlineStr"/>
       <c r="W318" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -28824,11 +27556,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V319" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V319" t="inlineStr"/>
       <c r="W319" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -28913,11 +27641,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V320" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V320" t="inlineStr"/>
       <c r="W320" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -29002,11 +27726,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V321" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V321" t="inlineStr"/>
       <c r="W321" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -29091,11 +27811,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V322" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V322" t="inlineStr"/>
       <c r="W322" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -29180,11 +27896,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V323" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V323" t="inlineStr"/>
       <c r="W323" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -29269,11 +27981,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V324" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V324" t="inlineStr"/>
       <c r="W324" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -29358,11 +28066,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V325" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V325" t="inlineStr"/>
       <c r="W325" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -29447,11 +28151,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V326" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V326" t="inlineStr"/>
       <c r="W326" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -29536,11 +28236,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V327" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V327" t="inlineStr"/>
       <c r="W327" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -29625,11 +28321,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V328" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V328" t="inlineStr"/>
       <c r="W328" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -29714,11 +28406,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V329" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V329" t="inlineStr"/>
       <c r="W329" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -29803,11 +28491,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V330" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V330" t="inlineStr"/>
       <c r="W330" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -29892,11 +28576,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V331" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V331" t="inlineStr"/>
       <c r="W331" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -29981,11 +28661,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V332" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V332" t="inlineStr"/>
       <c r="W332" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -30070,11 +28746,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V333" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V333" t="inlineStr"/>
       <c r="W333" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -30159,11 +28831,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V334" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V334" t="inlineStr"/>
       <c r="W334" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -30248,11 +28916,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V335" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V335" t="inlineStr"/>
       <c r="W335" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -30337,11 +29001,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V336" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V336" t="inlineStr"/>
       <c r="W336" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -30426,11 +29086,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V337" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V337" t="inlineStr"/>
       <c r="W337" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -30515,11 +29171,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V338" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V338" t="inlineStr"/>
       <c r="W338" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -30604,11 +29256,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V339" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V339" t="inlineStr"/>
       <c r="W339" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -30693,11 +29341,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V340" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V340" t="inlineStr"/>
       <c r="W340" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -30782,11 +29426,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V341" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V341" t="inlineStr"/>
       <c r="W341" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -30871,11 +29511,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V342" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V342" t="inlineStr"/>
       <c r="W342" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -30960,11 +29596,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V343" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V343" t="inlineStr"/>
       <c r="W343" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -31049,11 +29681,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V344" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V344" t="inlineStr"/>
       <c r="W344" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -31138,11 +29766,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V345" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V345" t="inlineStr"/>
       <c r="W345" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -31227,11 +29851,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V346" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V346" t="inlineStr"/>
       <c r="W346" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -31316,11 +29936,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V347" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V347" t="inlineStr"/>
       <c r="W347" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -31405,11 +30021,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V348" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V348" t="inlineStr"/>
       <c r="W348" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -31494,11 +30106,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V349" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V349" t="inlineStr"/>
       <c r="W349" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -31583,11 +30191,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V350" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V350" t="inlineStr"/>
       <c r="W350" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -31672,11 +30276,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V351" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V351" t="inlineStr"/>
       <c r="W351" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -31761,11 +30361,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V352" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V352" t="inlineStr"/>
       <c r="W352" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -31850,11 +30446,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V353" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V353" t="inlineStr"/>
       <c r="W353" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -31939,11 +30531,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V354" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V354" t="inlineStr"/>
       <c r="W354" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -32028,11 +30616,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V355" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V355" t="inlineStr"/>
       <c r="W355" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -32117,11 +30701,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V356" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V356" t="inlineStr"/>
       <c r="W356" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -32206,11 +30786,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V357" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V357" t="inlineStr"/>
       <c r="W357" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -32295,11 +30871,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V358" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V358" t="inlineStr"/>
       <c r="W358" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -32384,11 +30956,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V359" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V359" t="inlineStr"/>
       <c r="W359" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -32473,11 +31041,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V360" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V360" t="inlineStr"/>
       <c r="W360" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -32562,11 +31126,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V361" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V361" t="inlineStr"/>
       <c r="W361" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -32651,11 +31211,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V362" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V362" t="inlineStr"/>
       <c r="W362" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -32740,11 +31296,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V363" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V363" t="inlineStr"/>
       <c r="W363" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -32829,11 +31381,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V364" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V364" t="inlineStr"/>
       <c r="W364" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -32918,11 +31466,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V365" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V365" t="inlineStr"/>
       <c r="W365" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -33007,11 +31551,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V366" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V366" t="inlineStr"/>
       <c r="W366" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -33096,11 +31636,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V367" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V367" t="inlineStr"/>
       <c r="W367" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -33185,11 +31721,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V368" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V368" t="inlineStr"/>
       <c r="W368" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -33274,11 +31806,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V369" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V369" t="inlineStr"/>
       <c r="W369" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -33363,11 +31891,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V370" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V370" t="inlineStr"/>
       <c r="W370" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -33452,11 +31976,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V371" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V371" t="inlineStr"/>
       <c r="W371" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -33541,11 +32061,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V372" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V372" t="inlineStr"/>
       <c r="W372" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -33630,11 +32146,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V373" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V373" t="inlineStr"/>
       <c r="W373" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -33719,11 +32231,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V374" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V374" t="inlineStr"/>
       <c r="W374" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -33808,11 +32316,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V375" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V375" t="inlineStr"/>
       <c r="W375" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -33897,11 +32401,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V376" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V376" t="inlineStr"/>
       <c r="W376" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -33986,11 +32486,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V377" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V377" t="inlineStr"/>
       <c r="W377" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -34075,11 +32571,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V378" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V378" t="inlineStr"/>
       <c r="W378" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -34164,11 +32656,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V379" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V379" t="inlineStr"/>
       <c r="W379" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -34253,11 +32741,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V380" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V380" t="inlineStr"/>
       <c r="W380" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -34342,11 +32826,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V381" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V381" t="inlineStr"/>
       <c r="W381" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -34431,11 +32911,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V382" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V382" t="inlineStr"/>
       <c r="W382" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -34520,11 +32996,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V383" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V383" t="inlineStr"/>
       <c r="W383" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -34609,11 +33081,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V384" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V384" t="inlineStr"/>
       <c r="W384" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -34698,11 +33166,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V385" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V385" t="inlineStr"/>
       <c r="W385" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -34787,11 +33251,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V386" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V386" t="inlineStr"/>
       <c r="W386" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -34876,11 +33336,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V387" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V387" t="inlineStr"/>
       <c r="W387" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -34965,11 +33421,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V388" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V388" t="inlineStr"/>
       <c r="W388" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -35054,11 +33506,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V389" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V389" t="inlineStr"/>
       <c r="W389" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -35143,11 +33591,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V390" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V390" t="inlineStr"/>
       <c r="W390" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -35232,11 +33676,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V391" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V391" t="inlineStr"/>
       <c r="W391" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -35321,11 +33761,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V392" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V392" t="inlineStr"/>
       <c r="W392" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -35410,11 +33846,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V393" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V393" t="inlineStr"/>
       <c r="W393" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -35499,11 +33931,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V394" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V394" t="inlineStr"/>
       <c r="W394" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -35588,11 +34016,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V395" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V395" t="inlineStr"/>
       <c r="W395" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -35677,11 +34101,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V396" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V396" t="inlineStr"/>
       <c r="W396" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -35766,11 +34186,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V397" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V397" t="inlineStr"/>
       <c r="W397" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -35855,11 +34271,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V398" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V398" t="inlineStr"/>
       <c r="W398" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -35944,11 +34356,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V399" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V399" t="inlineStr"/>
       <c r="W399" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -36033,11 +34441,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V400" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V400" t="inlineStr"/>
       <c r="W400" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -36122,11 +34526,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V401" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V401" t="inlineStr"/>
       <c r="W401" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -36211,11 +34611,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V402" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V402" t="inlineStr"/>
       <c r="W402" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -36300,11 +34696,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V403" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V403" t="inlineStr"/>
       <c r="W403" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -36389,11 +34781,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V404" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V404" t="inlineStr"/>
       <c r="W404" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -36478,11 +34866,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V405" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V405" t="inlineStr"/>
       <c r="W405" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -36567,11 +34951,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V406" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V406" t="inlineStr"/>
       <c r="W406" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -36656,11 +35036,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V407" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V407" t="inlineStr"/>
       <c r="W407" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -36745,11 +35121,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V408" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V408" t="inlineStr"/>
       <c r="W408" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -36834,11 +35206,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V409" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V409" t="inlineStr"/>
       <c r="W409" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -36923,11 +35291,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V410" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V410" t="inlineStr"/>
       <c r="W410" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -37012,11 +35376,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V411" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V411" t="inlineStr"/>
       <c r="W411" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -37101,11 +35461,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V412" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V412" t="inlineStr"/>
       <c r="W412" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -37190,11 +35546,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V413" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V413" t="inlineStr"/>
       <c r="W413" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -37279,11 +35631,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V414" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V414" t="inlineStr"/>
       <c r="W414" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -37368,11 +35716,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V415" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V415" t="inlineStr"/>
       <c r="W415" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -37457,11 +35801,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V416" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V416" t="inlineStr"/>
       <c r="W416" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -37546,11 +35886,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V417" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V417" t="inlineStr"/>
       <c r="W417" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -37635,11 +35971,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V418" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V418" t="inlineStr"/>
       <c r="W418" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -37724,11 +36056,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V419" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V419" t="inlineStr"/>
       <c r="W419" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -37813,11 +36141,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V420" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V420" t="inlineStr"/>
       <c r="W420" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -37902,11 +36226,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V421" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V421" t="inlineStr"/>
       <c r="W421" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -37991,11 +36311,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V422" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V422" t="inlineStr"/>
       <c r="W422" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -38080,11 +36396,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V423" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V423" t="inlineStr"/>
       <c r="W423" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -38169,11 +36481,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V424" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V424" t="inlineStr"/>
       <c r="W424" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -38258,11 +36566,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V425" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V425" t="inlineStr"/>
       <c r="W425" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -38347,11 +36651,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V426" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V426" t="inlineStr"/>
       <c r="W426" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -38436,11 +36736,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V427" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V427" t="inlineStr"/>
       <c r="W427" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -38525,11 +36821,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V428" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V428" t="inlineStr"/>
       <c r="W428" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -38614,11 +36906,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V429" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V429" t="inlineStr"/>
       <c r="W429" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -38703,11 +36991,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V430" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V430" t="inlineStr"/>
       <c r="W430" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -38792,11 +37076,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V431" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V431" t="inlineStr"/>
       <c r="W431" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -38881,11 +37161,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V432" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V432" t="inlineStr"/>
       <c r="W432" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -38970,11 +37246,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V433" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V433" t="inlineStr"/>
       <c r="W433" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -39059,11 +37331,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V434" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V434" t="inlineStr"/>
       <c r="W434" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -39148,11 +37416,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V435" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V435" t="inlineStr"/>
       <c r="W435" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -39237,11 +37501,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V436" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V436" t="inlineStr"/>
       <c r="W436" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -39326,11 +37586,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V437" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V437" t="inlineStr"/>
       <c r="W437" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -39415,11 +37671,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V438" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V438" t="inlineStr"/>
       <c r="W438" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -39504,11 +37756,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V439" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V439" t="inlineStr"/>
       <c r="W439" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -39593,11 +37841,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V440" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V440" t="inlineStr"/>
       <c r="W440" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -39682,11 +37926,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V441" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V441" t="inlineStr"/>
       <c r="W441" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -39771,11 +38011,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V442" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V442" t="inlineStr"/>
       <c r="W442" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -39860,11 +38096,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V443" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V443" t="inlineStr"/>
       <c r="W443" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -39949,11 +38181,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V444" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V444" t="inlineStr"/>
       <c r="W444" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -40038,11 +38266,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V445" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V445" t="inlineStr"/>
       <c r="W445" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -40127,11 +38351,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V446" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V446" t="inlineStr"/>
       <c r="W446" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -40216,11 +38436,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V447" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V447" t="inlineStr"/>
       <c r="W447" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -40305,11 +38521,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V448" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V448" t="inlineStr"/>
       <c r="W448" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -40394,11 +38606,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V449" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V449" t="inlineStr"/>
       <c r="W449" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -40483,11 +38691,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V450" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V450" t="inlineStr"/>
       <c r="W450" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -40572,11 +38776,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V451" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V451" t="inlineStr"/>
       <c r="W451" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -40661,11 +38861,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V452" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V452" t="inlineStr"/>
       <c r="W452" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -40750,11 +38946,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V453" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V453" t="inlineStr"/>
       <c r="W453" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -40839,11 +39031,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V454" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V454" t="inlineStr"/>
       <c r="W454" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -40928,11 +39116,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V455" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V455" t="inlineStr"/>
       <c r="W455" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -41017,11 +39201,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V456" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V456" t="inlineStr"/>
       <c r="W456" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -41106,11 +39286,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V457" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V457" t="inlineStr"/>
       <c r="W457" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -41195,11 +39371,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V458" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V458" t="inlineStr"/>
       <c r="W458" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -41284,11 +39456,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V459" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V459" t="inlineStr"/>
       <c r="W459" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -41373,11 +39541,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V460" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V460" t="inlineStr"/>
       <c r="W460" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -41462,11 +39626,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V461" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V461" t="inlineStr"/>
       <c r="W461" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -41551,11 +39711,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V462" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V462" t="inlineStr"/>
       <c r="W462" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -41640,11 +39796,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V463" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V463" t="inlineStr"/>
       <c r="W463" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -41729,11 +39881,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V464" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V464" t="inlineStr"/>
       <c r="W464" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -41818,11 +39966,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V465" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V465" t="inlineStr"/>
       <c r="W465" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -41907,11 +40051,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V466" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V466" t="inlineStr"/>
       <c r="W466" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -41996,11 +40136,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V467" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V467" t="inlineStr"/>
       <c r="W467" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -42085,11 +40221,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V468" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V468" t="inlineStr"/>
       <c r="W468" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -42174,11 +40306,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V469" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V469" t="inlineStr"/>
       <c r="W469" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -42263,11 +40391,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V470" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V470" t="inlineStr"/>
       <c r="W470" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -42352,11 +40476,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V471" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V471" t="inlineStr"/>
       <c r="W471" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -42441,11 +40561,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V472" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V472" t="inlineStr"/>
       <c r="W472" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -42530,11 +40646,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V473" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V473" t="inlineStr"/>
       <c r="W473" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -42619,11 +40731,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V474" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V474" t="inlineStr"/>
       <c r="W474" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -42708,11 +40816,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V475" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V475" t="inlineStr"/>
       <c r="W475" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -42797,11 +40901,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V476" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V476" t="inlineStr"/>
       <c r="W476" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -42886,11 +40986,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V477" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V477" t="inlineStr"/>
       <c r="W477" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -42975,11 +41071,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V478" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V478" t="inlineStr"/>
       <c r="W478" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -43064,11 +41156,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V479" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V479" t="inlineStr"/>
       <c r="W479" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -43153,11 +41241,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V480" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V480" t="inlineStr"/>
       <c r="W480" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -43242,11 +41326,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V481" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V481" t="inlineStr"/>
       <c r="W481" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -43331,11 +41411,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V482" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V482" t="inlineStr"/>
       <c r="W482" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -43420,11 +41496,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V483" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V483" t="inlineStr"/>
       <c r="W483" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -43509,11 +41581,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V484" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V484" t="inlineStr"/>
       <c r="W484" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -43598,11 +41666,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V485" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V485" t="inlineStr"/>
       <c r="W485" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -43687,11 +41751,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V486" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V486" t="inlineStr"/>
       <c r="W486" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -43776,11 +41836,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V487" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V487" t="inlineStr"/>
       <c r="W487" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -43865,11 +41921,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V488" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V488" t="inlineStr"/>
       <c r="W488" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -43954,11 +42006,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V489" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V489" t="inlineStr"/>
       <c r="W489" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -44043,11 +42091,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V490" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V490" t="inlineStr"/>
       <c r="W490" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -44132,11 +42176,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V491" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V491" t="inlineStr"/>
       <c r="W491" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -44221,11 +42261,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V492" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V492" t="inlineStr"/>
       <c r="W492" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -44310,11 +42346,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V493" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V493" t="inlineStr"/>
       <c r="W493" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -44399,11 +42431,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V494" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V494" t="inlineStr"/>
       <c r="W494" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -44488,11 +42516,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V495" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V495" t="inlineStr"/>
       <c r="W495" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -44577,11 +42601,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V496" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V496" t="inlineStr"/>
       <c r="W496" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -44666,11 +42686,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V497" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V497" t="inlineStr"/>
       <c r="W497" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -44755,11 +42771,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V498" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V498" t="inlineStr"/>
       <c r="W498" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -44844,11 +42856,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V499" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V499" t="inlineStr"/>
       <c r="W499" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -44933,11 +42941,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V500" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V500" t="inlineStr"/>
       <c r="W500" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -45022,11 +43026,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V501" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V501" t="inlineStr"/>
       <c r="W501" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -45111,11 +43111,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V502" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V502" t="inlineStr"/>
       <c r="W502" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -45200,11 +43196,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V503" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V503" t="inlineStr"/>
       <c r="W503" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -45289,11 +43281,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V504" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V504" t="inlineStr"/>
       <c r="W504" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -45378,11 +43366,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V505" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V505" t="inlineStr"/>
       <c r="W505" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -45467,11 +43451,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V506" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V506" t="inlineStr"/>
       <c r="W506" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -45556,11 +43536,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V507" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V507" t="inlineStr"/>
       <c r="W507" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -45645,11 +43621,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V508" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V508" t="inlineStr"/>
       <c r="W508" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -45734,11 +43706,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V509" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V509" t="inlineStr"/>
       <c r="W509" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -45823,11 +43791,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V510" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V510" t="inlineStr"/>
       <c r="W510" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -45912,11 +43876,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V511" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V511" t="inlineStr"/>
       <c r="W511" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -46001,11 +43961,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V512" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V512" t="inlineStr"/>
       <c r="W512" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -46090,11 +44046,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V513" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V513" t="inlineStr"/>
       <c r="W513" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -46179,11 +44131,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V514" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V514" t="inlineStr"/>
       <c r="W514" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -46268,11 +44216,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V515" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V515" t="inlineStr"/>
       <c r="W515" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -46357,11 +44301,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V516" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V516" t="inlineStr"/>
       <c r="W516" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -46446,11 +44386,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V517" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V517" t="inlineStr"/>
       <c r="W517" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -46535,11 +44471,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V518" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V518" t="inlineStr"/>
       <c r="W518" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -46624,11 +44556,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V519" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V519" t="inlineStr"/>
       <c r="W519" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -46713,11 +44641,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V520" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V520" t="inlineStr"/>
       <c r="W520" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -46802,11 +44726,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V521" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V521" t="inlineStr"/>
       <c r="W521" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -46891,11 +44811,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V522" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V522" t="inlineStr"/>
       <c r="W522" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -46980,11 +44896,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V523" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V523" t="inlineStr"/>
       <c r="W523" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -47069,11 +44981,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V524" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V524" t="inlineStr"/>
       <c r="W524" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -47158,11 +45066,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V525" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V525" t="inlineStr"/>
       <c r="W525" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -47247,11 +45151,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V526" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V526" t="inlineStr"/>
       <c r="W526" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -47336,11 +45236,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V527" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V527" t="inlineStr"/>
       <c r="W527" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -47425,11 +45321,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V528" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V528" t="inlineStr"/>
       <c r="W528" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -47514,11 +45406,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V529" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V529" t="inlineStr"/>
       <c r="W529" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -47603,11 +45491,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V530" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V530" t="inlineStr"/>
       <c r="W530" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -47692,11 +45576,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V531" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V531" t="inlineStr"/>
       <c r="W531" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -47781,11 +45661,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V532" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V532" t="inlineStr"/>
       <c r="W532" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -47870,11 +45746,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V533" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V533" t="inlineStr"/>
       <c r="W533" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -47959,11 +45831,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V534" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V534" t="inlineStr"/>
       <c r="W534" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -48048,11 +45916,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V535" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V535" t="inlineStr"/>
       <c r="W535" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -48137,11 +46001,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V536" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V536" t="inlineStr"/>
       <c r="W536" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -48226,11 +46086,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V537" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V537" t="inlineStr"/>
       <c r="W537" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -48315,11 +46171,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V538" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V538" t="inlineStr"/>
       <c r="W538" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -48404,11 +46256,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V539" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V539" t="inlineStr"/>
       <c r="W539" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -48493,11 +46341,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V540" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V540" t="inlineStr"/>
       <c r="W540" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -48582,11 +46426,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V541" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V541" t="inlineStr"/>
       <c r="W541" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -48671,11 +46511,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V542" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V542" t="inlineStr"/>
       <c r="W542" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -48760,11 +46596,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V543" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V543" t="inlineStr"/>
       <c r="W543" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -48849,11 +46681,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V544" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V544" t="inlineStr"/>
       <c r="W544" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -48938,11 +46766,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V545" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V545" t="inlineStr"/>
       <c r="W545" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -49027,11 +46851,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V546" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V546" t="inlineStr"/>
       <c r="W546" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -49116,11 +46936,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V547" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V547" t="inlineStr"/>
       <c r="W547" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -49205,11 +47021,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V548" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V548" t="inlineStr"/>
       <c r="W548" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -49294,11 +47106,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V549" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V549" t="inlineStr"/>
       <c r="W549" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -49383,11 +47191,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V550" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V550" t="inlineStr"/>
       <c r="W550" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -49472,11 +47276,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V551" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V551" t="inlineStr"/>
       <c r="W551" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -49561,11 +47361,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V552" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V552" t="inlineStr"/>
       <c r="W552" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -49650,11 +47446,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V553" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V553" t="inlineStr"/>
       <c r="W553" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -49739,11 +47531,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V554" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V554" t="inlineStr"/>
       <c r="W554" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -49828,11 +47616,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V555" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V555" t="inlineStr"/>
       <c r="W555" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -49917,11 +47701,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V556" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V556" t="inlineStr"/>
       <c r="W556" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -50006,11 +47786,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V557" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V557" t="inlineStr"/>
       <c r="W557" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -50095,11 +47871,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V558" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V558" t="inlineStr"/>
       <c r="W558" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -50184,11 +47956,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V559" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V559" t="inlineStr"/>
       <c r="W559" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -50273,11 +48041,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V560" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V560" t="inlineStr"/>
       <c r="W560" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -50362,11 +48126,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V561" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V561" t="inlineStr"/>
       <c r="W561" t="inlineStr">
         <is>
           <t>IFIX</t>
@@ -50451,11 +48211,7 @@
           <t>0.90% a.a.</t>
         </is>
       </c>
-      <c r="V562" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="V562" t="inlineStr"/>
       <c r="W562" t="inlineStr">
         <is>
           <t>IFIX</t>

--- a/fiis_b3.xlsx
+++ b/fiis_b3.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -680,7 +680,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -765,7 +765,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S4" t="n">
@@ -850,7 +850,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S5" t="n">
@@ -935,7 +935,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S7" t="n">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S8" t="n">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S9" t="n">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S10" t="n">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S11" t="n">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S12" t="n">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S13" t="n">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S14" t="n">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual</t>
         </is>
       </c>
       <c r="S15" t="n">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual</t>
         </is>
       </c>
       <c r="S16" t="n">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual</t>
         </is>
       </c>
       <c r="S17" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual</t>
         </is>
       </c>
       <c r="S18" t="n">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual</t>
         </is>
       </c>
       <c r="S19" t="n">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S20" t="n">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S21" t="n">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S22" t="n">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S23" t="n">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S24" t="n">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S25" t="n">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S26" t="n">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S27" t="n">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S28" t="n">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S29" t="n">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S30" t="n">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S31" t="n">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S32" t="n">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S33" t="n">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S34" t="n">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BB Asset Management</t>
         </is>
       </c>
       <c r="S35" t="n">
@@ -3485,7 +3485,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BB Asset Management</t>
         </is>
       </c>
       <c r="S36" t="n">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BB Asset Management</t>
         </is>
       </c>
       <c r="S37" t="n">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BB Asset Management</t>
         </is>
       </c>
       <c r="S38" t="n">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BB Asset Management</t>
         </is>
       </c>
       <c r="S39" t="n">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BB Asset Management</t>
         </is>
       </c>
       <c r="S40" t="n">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BB Asset Management</t>
         </is>
       </c>
       <c r="S41" t="n">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual</t>
         </is>
       </c>
       <c r="S42" t="n">
@@ -4080,7 +4080,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual</t>
         </is>
       </c>
       <c r="S43" t="n">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual</t>
         </is>
       </c>
       <c r="S44" t="n">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S45" t="n">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S46" t="n">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S47" t="n">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S48" t="n">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S49" t="n">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S50" t="n">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S51" t="n">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S52" t="n">
@@ -4930,7 +4930,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S53" t="n">
@@ -5015,7 +5015,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S54" t="n">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S55" t="n">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S56" t="n">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S57" t="n">
@@ -5355,7 +5355,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S58" t="n">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S59" t="n">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S60" t="n">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S61" t="n">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S62" t="n">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S63" t="n">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual</t>
         </is>
       </c>
       <c r="S64" t="n">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual</t>
         </is>
       </c>
       <c r="S65" t="n">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual</t>
         </is>
       </c>
       <c r="S66" t="n">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual</t>
         </is>
       </c>
       <c r="S67" t="n">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual</t>
         </is>
       </c>
       <c r="S68" t="n">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual</t>
         </is>
       </c>
       <c r="S69" t="n">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual</t>
         </is>
       </c>
       <c r="S70" t="n">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual</t>
         </is>
       </c>
       <c r="S71" t="n">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual</t>
         </is>
       </c>
       <c r="S72" t="n">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual</t>
         </is>
       </c>
       <c r="S73" t="n">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual</t>
         </is>
       </c>
       <c r="S74" t="n">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual</t>
         </is>
       </c>
       <c r="S75" t="n">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual</t>
         </is>
       </c>
       <c r="S76" t="n">
@@ -6970,7 +6970,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual</t>
         </is>
       </c>
       <c r="S77" t="n">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual</t>
         </is>
       </c>
       <c r="S78" t="n">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual</t>
         </is>
       </c>
       <c r="S79" t="n">
@@ -7225,7 +7225,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual</t>
         </is>
       </c>
       <c r="S80" t="n">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual</t>
         </is>
       </c>
       <c r="S81" t="n">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual</t>
         </is>
       </c>
       <c r="S82" t="n">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S83" t="n">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S84" t="n">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S85" t="n">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S86" t="n">
@@ -7820,7 +7820,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S87" t="n">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S88" t="n">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S89" t="n">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S90" t="n">
@@ -8160,7 +8160,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S91" t="n">
@@ -8245,7 +8245,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S92" t="n">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S93" t="n">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S94" t="n">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S95" t="n">
@@ -8585,7 +8585,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S96" t="n">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S97" t="n">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual</t>
         </is>
       </c>
       <c r="S98" t="n">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual</t>
         </is>
       </c>
       <c r="S99" t="n">
@@ -8925,7 +8925,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual</t>
         </is>
       </c>
       <c r="S100" t="n">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual</t>
         </is>
       </c>
       <c r="S101" t="n">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual</t>
         </is>
       </c>
       <c r="S102" t="n">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual</t>
         </is>
       </c>
       <c r="S103" t="n">
@@ -9265,7 +9265,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual</t>
         </is>
       </c>
       <c r="S104" t="n">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S105" t="n">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S106" t="n">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S107" t="n">
@@ -9605,7 +9605,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S108" t="n">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Caixa Econômica Federal</t>
         </is>
       </c>
       <c r="S109" t="n">
@@ -9775,7 +9775,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Caixa Econômica Federal</t>
         </is>
       </c>
       <c r="S110" t="n">
@@ -9860,7 +9860,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Caixa Econômica Federal</t>
         </is>
       </c>
       <c r="S111" t="n">
@@ -9945,7 +9945,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Caixa Econômica Federal</t>
         </is>
       </c>
       <c r="S112" t="n">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Caixa Econômica Federal</t>
         </is>
       </c>
       <c r="S113" t="n">
@@ -10115,7 +10115,7 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Caixa Econômica Federal</t>
         </is>
       </c>
       <c r="S114" t="n">
@@ -10200,7 +10200,7 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S115" t="n">
@@ -10285,7 +10285,7 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S116" t="n">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S117" t="n">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S118" t="n">
@@ -10540,7 +10540,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S119" t="n">
@@ -10625,7 +10625,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Vortx</t>
         </is>
       </c>
       <c r="S120" t="n">
@@ -10710,7 +10710,7 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S121" t="n">
@@ -10795,7 +10795,7 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S122" t="n">
@@ -10880,7 +10880,7 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S123" t="n">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S124" t="n">
@@ -11050,7 +11050,7 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S125" t="n">
@@ -11135,7 +11135,7 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S126" t="n">
@@ -11220,7 +11220,7 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S127" t="n">
@@ -11305,7 +11305,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S128" t="n">
@@ -11390,7 +11390,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S129" t="n">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S130" t="n">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S131" t="n">
@@ -11645,7 +11645,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S132" t="n">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S133" t="n">
@@ -11815,7 +11815,7 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S134" t="n">
@@ -11900,7 +11900,7 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S135" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S136" t="n">
@@ -12070,7 +12070,7 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S137" t="n">
@@ -12155,7 +12155,7 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S138" t="n">
@@ -12240,7 +12240,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S139" t="n">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S140" t="n">
@@ -12410,7 +12410,7 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S141" t="n">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S142" t="n">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S143" t="n">
@@ -12665,7 +12665,7 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S144" t="n">
@@ -12750,7 +12750,7 @@
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S145" t="n">
@@ -12835,7 +12835,7 @@
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S146" t="n">
@@ -12920,7 +12920,7 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S147" t="n">
@@ -13005,7 +13005,7 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S148" t="n">
@@ -13090,7 +13090,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S149" t="n">
@@ -13175,7 +13175,7 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S150" t="n">
@@ -13260,7 +13260,7 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S151" t="n">
@@ -13345,7 +13345,7 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S152" t="n">
@@ -13430,7 +13430,7 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S153" t="n">
@@ -13515,7 +13515,7 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S154" t="n">
@@ -13600,7 +13600,7 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S155" t="n">
@@ -13685,7 +13685,7 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S156" t="n">
@@ -13770,7 +13770,7 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S157" t="n">
@@ -13855,7 +13855,7 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S158" t="n">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S159" t="n">
@@ -14025,7 +14025,7 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S160" t="n">
@@ -14110,7 +14110,7 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S161" t="n">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S162" t="n">
@@ -14280,7 +14280,7 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S163" t="n">
@@ -14365,7 +14365,7 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S164" t="n">
@@ -14450,7 +14450,7 @@
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S165" t="n">
@@ -14535,7 +14535,7 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S166" t="n">
@@ -14620,7 +14620,7 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S167" t="n">
@@ -14705,7 +14705,7 @@
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S168" t="n">
@@ -14790,7 +14790,7 @@
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S169" t="n">
@@ -14875,7 +14875,7 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S170" t="n">
@@ -14960,7 +14960,7 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S171" t="n">
@@ -15045,7 +15045,7 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S172" t="n">
@@ -15130,7 +15130,7 @@
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S173" t="n">
@@ -15215,7 +15215,7 @@
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S174" t="n">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S175" t="n">
@@ -15385,7 +15385,7 @@
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S176" t="n">
@@ -15470,7 +15470,7 @@
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S177" t="n">
@@ -15555,7 +15555,7 @@
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S178" t="n">
@@ -15640,7 +15640,7 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S179" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S180" t="n">
@@ -15810,7 +15810,7 @@
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S181" t="n">
@@ -15895,7 +15895,7 @@
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S182" t="n">
@@ -15980,7 +15980,7 @@
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S183" t="n">
@@ -16065,7 +16065,7 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S184" t="n">
@@ -16150,7 +16150,7 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S185" t="n">
@@ -16235,7 +16235,7 @@
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S186" t="n">
@@ -16320,7 +16320,7 @@
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S187" t="n">
@@ -16405,7 +16405,7 @@
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S188" t="n">
@@ -16490,7 +16490,7 @@
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S189" t="n">
@@ -16575,7 +16575,7 @@
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S190" t="n">
@@ -16660,7 +16660,7 @@
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S191" t="n">
@@ -16745,7 +16745,7 @@
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S192" t="n">
@@ -16830,7 +16830,7 @@
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S193" t="n">
@@ -16915,7 +16915,7 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S194" t="n">
@@ -17000,7 +17000,7 @@
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S195" t="n">
@@ -17085,7 +17085,7 @@
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S196" t="n">
@@ -17170,7 +17170,7 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S197" t="n">
@@ -17255,7 +17255,7 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S198" t="n">
@@ -17340,7 +17340,7 @@
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S199" t="n">
@@ -17425,7 +17425,7 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Hedge Investments</t>
         </is>
       </c>
       <c r="S200" t="n">
@@ -17510,7 +17510,7 @@
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Credit Suisse (CSHG) / Pátria</t>
         </is>
       </c>
       <c r="S201" t="n">
@@ -17595,7 +17595,7 @@
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Credit Suisse (CSHG) / Pátria</t>
         </is>
       </c>
       <c r="S202" t="n">
@@ -17680,7 +17680,7 @@
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Credit Suisse (CSHG) / Pátria</t>
         </is>
       </c>
       <c r="S203" t="n">
@@ -17765,7 +17765,7 @@
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Credit Suisse (CSHG) / Pátria</t>
         </is>
       </c>
       <c r="S204" t="n">
@@ -17850,7 +17850,7 @@
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Credit Suisse (CSHG) / Pátria</t>
         </is>
       </c>
       <c r="S205" t="n">
@@ -17935,7 +17935,7 @@
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Credit Suisse (CSHG) / Pátria</t>
         </is>
       </c>
       <c r="S206" t="n">
@@ -18020,7 +18020,7 @@
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Credit Suisse (CSHG) / Pátria</t>
         </is>
       </c>
       <c r="S207" t="n">
@@ -18105,7 +18105,7 @@
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Credit Suisse (CSHG) / Pátria</t>
         </is>
       </c>
       <c r="S208" t="n">
@@ -18190,7 +18190,7 @@
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Credit Suisse (CSHG) / Pátria</t>
         </is>
       </c>
       <c r="S209" t="n">
@@ -18275,7 +18275,7 @@
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Credit Suisse (CSHG) / Pátria</t>
         </is>
       </c>
       <c r="S210" t="n">
@@ -18360,7 +18360,7 @@
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Credit Suisse (CSHG) / Pátria</t>
         </is>
       </c>
       <c r="S211" t="n">
@@ -18445,7 +18445,7 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S212" t="n">
@@ -18530,7 +18530,7 @@
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S213" t="n">
@@ -18615,7 +18615,7 @@
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S214" t="n">
@@ -18700,7 +18700,7 @@
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S215" t="n">
@@ -18785,7 +18785,7 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S216" t="n">
@@ -18870,7 +18870,7 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S217" t="n">
@@ -18955,7 +18955,7 @@
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S218" t="n">
@@ -19040,7 +19040,7 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S219" t="n">
@@ -19125,7 +19125,7 @@
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S220" t="n">
@@ -19210,7 +19210,7 @@
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S221" t="n">
@@ -19295,7 +19295,7 @@
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S222" t="n">
@@ -19380,7 +19380,7 @@
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Mata de Santa Fé</t>
         </is>
       </c>
       <c r="S223" t="n">
@@ -19465,7 +19465,7 @@
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Mata de Santa Fé</t>
         </is>
       </c>
       <c r="S224" t="n">
@@ -19550,7 +19550,7 @@
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Mata de Santa Fé</t>
         </is>
       </c>
       <c r="S225" t="n">
@@ -19635,7 +19635,7 @@
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Mata de Santa Fé</t>
         </is>
       </c>
       <c r="S226" t="n">
@@ -19720,7 +19720,7 @@
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S227" t="n">
@@ -19805,7 +19805,7 @@
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S228" t="n">
@@ -19890,7 +19890,7 @@
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S229" t="n">
@@ -19975,7 +19975,7 @@
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S230" t="n">
@@ -20060,7 +20060,7 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S231" t="n">
@@ -20145,7 +20145,7 @@
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S232" t="n">
@@ -20230,7 +20230,7 @@
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S233" t="n">
@@ -20315,7 +20315,7 @@
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S234" t="n">
@@ -20400,7 +20400,7 @@
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S235" t="n">
@@ -20485,7 +20485,7 @@
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S236" t="n">
@@ -20570,7 +20570,7 @@
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S237" t="n">
@@ -20655,7 +20655,7 @@
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S238" t="n">
@@ -20740,7 +20740,7 @@
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S239" t="n">
@@ -20825,7 +20825,7 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S240" t="n">
@@ -20910,7 +20910,7 @@
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S241" t="n">
@@ -20995,7 +20995,7 @@
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S242" t="n">
@@ -21080,7 +21080,7 @@
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S243" t="n">
@@ -21165,7 +21165,7 @@
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S244" t="n">
@@ -21250,7 +21250,7 @@
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S245" t="n">
@@ -21335,7 +21335,7 @@
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual</t>
         </is>
       </c>
       <c r="S246" t="n">
@@ -21420,7 +21420,7 @@
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual</t>
         </is>
       </c>
       <c r="S247" t="n">
@@ -21505,7 +21505,7 @@
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S248" t="n">
@@ -21590,7 +21590,7 @@
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Itaú DTVM</t>
         </is>
       </c>
       <c r="S249" t="n">
@@ -21675,7 +21675,7 @@
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Itaú DTVM</t>
         </is>
       </c>
       <c r="S250" t="n">
@@ -21760,7 +21760,7 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Itaú DTVM</t>
         </is>
       </c>
       <c r="S251" t="n">
@@ -21845,7 +21845,7 @@
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S252" t="n">
@@ -21930,7 +21930,7 @@
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S253" t="n">
@@ -22015,7 +22015,7 @@
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S254" t="n">
@@ -22100,7 +22100,7 @@
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S255" t="n">
@@ -22185,7 +22185,7 @@
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S256" t="n">
@@ -22270,7 +22270,7 @@
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S257" t="n">
@@ -22355,7 +22355,7 @@
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S258" t="n">
@@ -22440,7 +22440,7 @@
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S259" t="n">
@@ -22525,7 +22525,7 @@
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S260" t="n">
@@ -22610,7 +22610,7 @@
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Banco Genial</t>
         </is>
       </c>
       <c r="S261" t="n">
@@ -22695,7 +22695,7 @@
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Banco Genial</t>
         </is>
       </c>
       <c r="S262" t="n">
@@ -22780,7 +22780,7 @@
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Banco Genial</t>
         </is>
       </c>
       <c r="S263" t="n">
@@ -22865,7 +22865,7 @@
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S264" t="n">
@@ -22950,7 +22950,7 @@
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S265" t="n">
@@ -23035,7 +23035,7 @@
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S266" t="n">
@@ -23120,7 +23120,7 @@
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S267" t="n">
@@ -23205,7 +23205,7 @@
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S268" t="n">
@@ -23290,7 +23290,7 @@
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S269" t="n">
@@ -23375,7 +23375,7 @@
       </c>
       <c r="R270" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S270" t="n">
@@ -23460,7 +23460,7 @@
       </c>
       <c r="R271" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S271" t="n">
@@ -23545,7 +23545,7 @@
       </c>
       <c r="R272" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Kinea / Intrag</t>
         </is>
       </c>
       <c r="S272" t="n">
@@ -23630,7 +23630,7 @@
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Kinea / Intrag</t>
         </is>
       </c>
       <c r="S273" t="n">
@@ -23715,7 +23715,7 @@
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Kinea / Intrag</t>
         </is>
       </c>
       <c r="S274" t="n">
@@ -23800,7 +23800,7 @@
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Kinea / Intrag</t>
         </is>
       </c>
       <c r="S275" t="n">
@@ -23885,7 +23885,7 @@
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Kinea / Intrag</t>
         </is>
       </c>
       <c r="S276" t="n">
@@ -23970,7 +23970,7 @@
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Kinea / Intrag</t>
         </is>
       </c>
       <c r="S277" t="n">
@@ -24055,7 +24055,7 @@
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Kinea / Intrag</t>
         </is>
       </c>
       <c r="S278" t="n">
@@ -24140,7 +24140,7 @@
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Kinea / Intrag</t>
         </is>
       </c>
       <c r="S279" t="n">
@@ -24225,7 +24225,7 @@
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Kinea / Intrag</t>
         </is>
       </c>
       <c r="S280" t="n">
@@ -24310,7 +24310,7 @@
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Kinea / Intrag</t>
         </is>
       </c>
       <c r="S281" t="n">
@@ -24395,7 +24395,7 @@
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S282" t="n">
@@ -24480,7 +24480,7 @@
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S283" t="n">
@@ -24565,7 +24565,7 @@
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S284" t="n">
@@ -24650,7 +24650,7 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S285" t="n">
@@ -24735,7 +24735,7 @@
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S286" t="n">
@@ -24820,7 +24820,7 @@
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S287" t="n">
@@ -24905,7 +24905,7 @@
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S288" t="n">
@@ -24990,7 +24990,7 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S289" t="n">
@@ -25075,7 +25075,7 @@
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S290" t="n">
@@ -25160,7 +25160,7 @@
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S291" t="n">
@@ -25245,7 +25245,7 @@
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S292" t="n">
@@ -25330,7 +25330,7 @@
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S293" t="n">
@@ -25415,7 +25415,7 @@
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S294" t="n">
@@ -25500,7 +25500,7 @@
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S295" t="n">
@@ -25585,7 +25585,7 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S296" t="n">
@@ -25670,7 +25670,7 @@
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S297" t="n">
@@ -25755,7 +25755,7 @@
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S298" t="n">
@@ -25840,7 +25840,7 @@
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S299" t="n">
@@ -25925,7 +25925,7 @@
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S300" t="n">
@@ -26010,7 +26010,7 @@
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S301" t="n">
@@ -26095,7 +26095,7 @@
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Vortx</t>
         </is>
       </c>
       <c r="S302" t="n">
@@ -26180,7 +26180,7 @@
       </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Mata de Santa Fé</t>
         </is>
       </c>
       <c r="S303" t="n">
@@ -26265,7 +26265,7 @@
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Mata de Santa Fé</t>
         </is>
       </c>
       <c r="S304" t="n">
@@ -26350,7 +26350,7 @@
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Mata de Santa Fé</t>
         </is>
       </c>
       <c r="S305" t="n">
@@ -26435,7 +26435,7 @@
       </c>
       <c r="R306" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Mata de Santa Fé</t>
         </is>
       </c>
       <c r="S306" t="n">
@@ -26520,7 +26520,7 @@
       </c>
       <c r="R307" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S307" t="n">
@@ -26605,7 +26605,7 @@
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Credit Suisse (CSHG) / Pátria</t>
         </is>
       </c>
       <c r="S308" t="n">
@@ -26690,7 +26690,7 @@
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Credit Suisse (CSHG) / Pátria</t>
         </is>
       </c>
       <c r="S309" t="n">
@@ -26775,7 +26775,7 @@
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Credit Suisse (CSHG) / Pátria</t>
         </is>
       </c>
       <c r="S310" t="n">
@@ -26860,7 +26860,7 @@
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Credit Suisse (CSHG) / Pátria</t>
         </is>
       </c>
       <c r="S311" t="n">
@@ -26945,7 +26945,7 @@
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Credit Suisse (CSHG) / Pátria</t>
         </is>
       </c>
       <c r="S312" t="n">
@@ -27030,7 +27030,7 @@
       </c>
       <c r="R313" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Credit Suisse (CSHG) / Pátria</t>
         </is>
       </c>
       <c r="S313" t="n">
@@ -27115,7 +27115,7 @@
       </c>
       <c r="R314" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S314" t="n">
@@ -27200,7 +27200,7 @@
       </c>
       <c r="R315" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S315" t="n">
@@ -27285,7 +27285,7 @@
       </c>
       <c r="R316" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S316" t="n">
@@ -27370,7 +27370,7 @@
       </c>
       <c r="R317" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S317" t="n">
@@ -27455,7 +27455,7 @@
       </c>
       <c r="R318" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S318" t="n">
@@ -27540,7 +27540,7 @@
       </c>
       <c r="R319" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S319" t="n">
@@ -27625,7 +27625,7 @@
       </c>
       <c r="R320" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S320" t="n">
@@ -27710,7 +27710,7 @@
       </c>
       <c r="R321" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S321" t="n">
@@ -27795,7 +27795,7 @@
       </c>
       <c r="R322" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S322" t="n">
@@ -27880,7 +27880,7 @@
       </c>
       <c r="R323" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S323" t="n">
@@ -27965,7 +27965,7 @@
       </c>
       <c r="R324" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S324" t="n">
@@ -28050,7 +28050,7 @@
       </c>
       <c r="R325" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S325" t="n">
@@ -28135,7 +28135,7 @@
       </c>
       <c r="R326" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S326" t="n">
@@ -28220,7 +28220,7 @@
       </c>
       <c r="R327" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual</t>
         </is>
       </c>
       <c r="S327" t="n">
@@ -28305,7 +28305,7 @@
       </c>
       <c r="R328" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S328" t="n">
@@ -28390,7 +28390,7 @@
       </c>
       <c r="R329" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S329" t="n">
@@ -28475,7 +28475,7 @@
       </c>
       <c r="R330" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S330" t="n">
@@ -28560,7 +28560,7 @@
       </c>
       <c r="R331" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S331" t="n">
@@ -28645,7 +28645,7 @@
       </c>
       <c r="R332" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S332" t="n">
@@ -28730,7 +28730,7 @@
       </c>
       <c r="R333" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S333" t="n">
@@ -28815,7 +28815,7 @@
       </c>
       <c r="R334" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S334" t="n">
@@ -28900,7 +28900,7 @@
       </c>
       <c r="R335" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S335" t="n">
@@ -28985,7 +28985,7 @@
       </c>
       <c r="R336" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S336" t="n">
@@ -29070,7 +29070,7 @@
       </c>
       <c r="R337" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S337" t="n">
@@ -29155,7 +29155,7 @@
       </c>
       <c r="R338" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S338" t="n">
@@ -29240,7 +29240,7 @@
       </c>
       <c r="R339" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S339" t="n">
@@ -29325,7 +29325,7 @@
       </c>
       <c r="R340" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S340" t="n">
@@ -29410,7 +29410,7 @@
       </c>
       <c r="R341" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S341" t="n">
@@ -29495,7 +29495,7 @@
       </c>
       <c r="R342" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S342" t="n">
@@ -29580,7 +29580,7 @@
       </c>
       <c r="R343" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S343" t="n">
@@ -29665,7 +29665,7 @@
       </c>
       <c r="R344" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S344" t="n">
@@ -29750,7 +29750,7 @@
       </c>
       <c r="R345" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S345" t="n">
@@ -29835,7 +29835,7 @@
       </c>
       <c r="R346" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S346" t="n">
@@ -29920,7 +29920,7 @@
       </c>
       <c r="R347" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Ourinvest</t>
         </is>
       </c>
       <c r="S347" t="n">
@@ -30005,7 +30005,7 @@
       </c>
       <c r="R348" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Ourinvest</t>
         </is>
       </c>
       <c r="S348" t="n">
@@ -30090,7 +30090,7 @@
       </c>
       <c r="R349" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Ourinvest</t>
         </is>
       </c>
       <c r="S349" t="n">
@@ -30175,7 +30175,7 @@
       </c>
       <c r="R350" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Ourinvest</t>
         </is>
       </c>
       <c r="S350" t="n">
@@ -30260,7 +30260,7 @@
       </c>
       <c r="R351" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Ourinvest</t>
         </is>
       </c>
       <c r="S351" t="n">
@@ -30345,7 +30345,7 @@
       </c>
       <c r="R352" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S352" t="n">
@@ -30430,7 +30430,7 @@
       </c>
       <c r="R353" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S353" t="n">
@@ -30515,7 +30515,7 @@
       </c>
       <c r="R354" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S354" t="n">
@@ -30600,7 +30600,7 @@
       </c>
       <c r="R355" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S355" t="n">
@@ -30685,7 +30685,7 @@
       </c>
       <c r="R356" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S356" t="n">
@@ -30770,7 +30770,7 @@
       </c>
       <c r="R357" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S357" t="n">
@@ -30855,7 +30855,7 @@
       </c>
       <c r="R358" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S358" t="n">
@@ -30940,7 +30940,7 @@
       </c>
       <c r="R359" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S359" t="n">
@@ -31025,7 +31025,7 @@
       </c>
       <c r="R360" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Plural Rendimento</t>
         </is>
       </c>
       <c r="S360" t="n">
@@ -31110,7 +31110,7 @@
       </c>
       <c r="R361" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Plural Rendimento</t>
         </is>
       </c>
       <c r="S361" t="n">
@@ -31195,7 +31195,7 @@
       </c>
       <c r="R362" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Plural Rendimento</t>
         </is>
       </c>
       <c r="S362" t="n">
@@ -31280,7 +31280,7 @@
       </c>
       <c r="R363" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Plural Rendimento</t>
         </is>
       </c>
       <c r="S363" t="n">
@@ -31365,7 +31365,7 @@
       </c>
       <c r="R364" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Plural Rendimento</t>
         </is>
       </c>
       <c r="S364" t="n">
@@ -31450,7 +31450,7 @@
       </c>
       <c r="R365" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S365" t="n">
@@ -31535,7 +31535,7 @@
       </c>
       <c r="R366" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S366" t="n">
@@ -31620,7 +31620,7 @@
       </c>
       <c r="R367" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S367" t="n">
@@ -31705,7 +31705,7 @@
       </c>
       <c r="R368" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S368" t="n">
@@ -31790,7 +31790,7 @@
       </c>
       <c r="R369" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S369" t="n">
@@ -31875,7 +31875,7 @@
       </c>
       <c r="R370" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S370" t="n">
@@ -31960,7 +31960,7 @@
       </c>
       <c r="R371" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S371" t="n">
@@ -32045,7 +32045,7 @@
       </c>
       <c r="R372" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S372" t="n">
@@ -32130,7 +32130,7 @@
       </c>
       <c r="R373" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S373" t="n">
@@ -32215,7 +32215,7 @@
       </c>
       <c r="R374" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S374" t="n">
@@ -32300,7 +32300,7 @@
       </c>
       <c r="R375" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S375" t="n">
@@ -32385,7 +32385,7 @@
       </c>
       <c r="R376" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S376" t="n">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="R377" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S377" t="n">
@@ -32555,7 +32555,7 @@
       </c>
       <c r="R378" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S378" t="n">
@@ -32640,7 +32640,7 @@
       </c>
       <c r="R379" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S379" t="n">
@@ -32725,7 +32725,7 @@
       </c>
       <c r="R380" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S380" t="n">
@@ -32810,7 +32810,7 @@
       </c>
       <c r="R381" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Vortx</t>
         </is>
       </c>
       <c r="S381" t="n">
@@ -32895,7 +32895,7 @@
       </c>
       <c r="R382" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S382" t="n">
@@ -32980,7 +32980,7 @@
       </c>
       <c r="R383" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S383" t="n">
@@ -33065,7 +33065,7 @@
       </c>
       <c r="R384" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S384" t="n">
@@ -33150,7 +33150,7 @@
       </c>
       <c r="R385" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S385" t="n">
@@ -33235,7 +33235,7 @@
       </c>
       <c r="R386" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S386" t="n">
@@ -33320,7 +33320,7 @@
       </c>
       <c r="R387" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / BRL Trust</t>
         </is>
       </c>
       <c r="S387" t="n">
@@ -33405,7 +33405,7 @@
       </c>
       <c r="R388" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / BRL Trust</t>
         </is>
       </c>
       <c r="S388" t="n">
@@ -33490,7 +33490,7 @@
       </c>
       <c r="R389" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / BRL Trust</t>
         </is>
       </c>
       <c r="S389" t="n">
@@ -33575,7 +33575,7 @@
       </c>
       <c r="R390" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / BRL Trust</t>
         </is>
       </c>
       <c r="S390" t="n">
@@ -33660,7 +33660,7 @@
       </c>
       <c r="R391" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / BRL Trust</t>
         </is>
       </c>
       <c r="S391" t="n">
@@ -33745,7 +33745,7 @@
       </c>
       <c r="R392" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / BRL Trust</t>
         </is>
       </c>
       <c r="S392" t="n">
@@ -33830,7 +33830,7 @@
       </c>
       <c r="R393" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / BRL Trust</t>
         </is>
       </c>
       <c r="S393" t="n">
@@ -33915,7 +33915,7 @@
       </c>
       <c r="R394" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / BRL Trust</t>
         </is>
       </c>
       <c r="S394" t="n">
@@ -34000,7 +34000,7 @@
       </c>
       <c r="R395" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / BRL Trust</t>
         </is>
       </c>
       <c r="S395" t="n">
@@ -34085,7 +34085,7 @@
       </c>
       <c r="R396" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / BRL Trust</t>
         </is>
       </c>
       <c r="S396" t="n">
@@ -34170,7 +34170,7 @@
       </c>
       <c r="R397" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / BRL Trust</t>
         </is>
       </c>
       <c r="S397" t="n">
@@ -34255,7 +34255,7 @@
       </c>
       <c r="R398" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / BRL Trust</t>
         </is>
       </c>
       <c r="S398" t="n">
@@ -34340,7 +34340,7 @@
       </c>
       <c r="R399" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / BRL Trust</t>
         </is>
       </c>
       <c r="S399" t="n">
@@ -34425,7 +34425,7 @@
       </c>
       <c r="R400" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / BRL Trust</t>
         </is>
       </c>
       <c r="S400" t="n">
@@ -34510,7 +34510,7 @@
       </c>
       <c r="R401" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / BRL Trust</t>
         </is>
       </c>
       <c r="S401" t="n">
@@ -34595,7 +34595,7 @@
       </c>
       <c r="R402" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / BRL Trust</t>
         </is>
       </c>
       <c r="S402" t="n">
@@ -34680,7 +34680,7 @@
       </c>
       <c r="R403" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / BRL Trust</t>
         </is>
       </c>
       <c r="S403" t="n">
@@ -34765,7 +34765,7 @@
       </c>
       <c r="R404" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / BRL Trust</t>
         </is>
       </c>
       <c r="S404" t="n">
@@ -34850,7 +34850,7 @@
       </c>
       <c r="R405" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / BRL Trust</t>
         </is>
       </c>
       <c r="S405" t="n">
@@ -34935,7 +34935,7 @@
       </c>
       <c r="R406" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / BRL Trust</t>
         </is>
       </c>
       <c r="S406" t="n">
@@ -35020,7 +35020,7 @@
       </c>
       <c r="R407" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / BRL Trust</t>
         </is>
       </c>
       <c r="S407" t="n">
@@ -35105,7 +35105,7 @@
       </c>
       <c r="R408" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / BRL Trust</t>
         </is>
       </c>
       <c r="S408" t="n">
@@ -35190,7 +35190,7 @@
       </c>
       <c r="R409" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / BRL Trust</t>
         </is>
       </c>
       <c r="S409" t="n">
@@ -35275,7 +35275,7 @@
       </c>
       <c r="R410" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / BRL Trust</t>
         </is>
       </c>
       <c r="S410" t="n">
@@ -35360,7 +35360,7 @@
       </c>
       <c r="R411" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / BRL Trust</t>
         </is>
       </c>
       <c r="S411" t="n">
@@ -35445,7 +35445,7 @@
       </c>
       <c r="R412" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / BRL Trust</t>
         </is>
       </c>
       <c r="S412" t="n">
@@ -35530,7 +35530,7 @@
       </c>
       <c r="R413" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / BRL Trust</t>
         </is>
       </c>
       <c r="S413" t="n">
@@ -35615,7 +35615,7 @@
       </c>
       <c r="R414" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S414" t="n">
@@ -35700,7 +35700,7 @@
       </c>
       <c r="R415" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S415" t="n">
@@ -35785,7 +35785,7 @@
       </c>
       <c r="R416" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S416" t="n">
@@ -35870,7 +35870,7 @@
       </c>
       <c r="R417" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S417" t="n">
@@ -35955,7 +35955,7 @@
       </c>
       <c r="R418" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S418" t="n">
@@ -36040,7 +36040,7 @@
       </c>
       <c r="R419" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S419" t="n">
@@ -36125,7 +36125,7 @@
       </c>
       <c r="R420" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S420" t="n">
@@ -36210,7 +36210,7 @@
       </c>
       <c r="R421" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BRL Trust</t>
         </is>
       </c>
       <c r="S421" t="n">
@@ -36295,7 +36295,7 @@
       </c>
       <c r="R422" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BRL Trust</t>
         </is>
       </c>
       <c r="S422" t="n">
@@ -36380,7 +36380,7 @@
       </c>
       <c r="R423" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BRL Trust</t>
         </is>
       </c>
       <c r="S423" t="n">
@@ -36465,7 +36465,7 @@
       </c>
       <c r="R424" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BRL Trust</t>
         </is>
       </c>
       <c r="S424" t="n">
@@ -36550,7 +36550,7 @@
       </c>
       <c r="R425" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BRL Trust</t>
         </is>
       </c>
       <c r="S425" t="n">
@@ -36635,7 +36635,7 @@
       </c>
       <c r="R426" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BRL Trust</t>
         </is>
       </c>
       <c r="S426" t="n">
@@ -36720,7 +36720,7 @@
       </c>
       <c r="R427" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BRL Trust</t>
         </is>
       </c>
       <c r="S427" t="n">
@@ -36805,7 +36805,7 @@
       </c>
       <c r="R428" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BRL Trust</t>
         </is>
       </c>
       <c r="S428" t="n">
@@ -36890,7 +36890,7 @@
       </c>
       <c r="R429" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BRL Trust</t>
         </is>
       </c>
       <c r="S429" t="n">
@@ -36975,7 +36975,7 @@
       </c>
       <c r="R430" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S430" t="n">
@@ -37060,7 +37060,7 @@
       </c>
       <c r="R431" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S431" t="n">
@@ -37145,7 +37145,7 @@
       </c>
       <c r="R432" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S432" t="n">
@@ -37230,7 +37230,7 @@
       </c>
       <c r="R433" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S433" t="n">
@@ -37315,7 +37315,7 @@
       </c>
       <c r="R434" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S434" t="n">
@@ -37400,7 +37400,7 @@
       </c>
       <c r="R435" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S435" t="n">
@@ -37485,7 +37485,7 @@
       </c>
       <c r="R436" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S436" t="n">
@@ -37570,7 +37570,7 @@
       </c>
       <c r="R437" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S437" t="n">
@@ -37655,7 +37655,7 @@
       </c>
       <c r="R438" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S438" t="n">
@@ -37740,7 +37740,7 @@
       </c>
       <c r="R439" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S439" t="n">
@@ -37825,7 +37825,7 @@
       </c>
       <c r="R440" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S440" t="n">
@@ -37910,7 +37910,7 @@
       </c>
       <c r="R441" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Itaú DTVM</t>
         </is>
       </c>
       <c r="S441" t="n">
@@ -37995,7 +37995,7 @@
       </c>
       <c r="R442" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S442" t="n">
@@ -38080,7 +38080,7 @@
       </c>
       <c r="R443" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Riza Asset</t>
         </is>
       </c>
       <c r="S443" t="n">
@@ -38165,7 +38165,7 @@
       </c>
       <c r="R444" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Riza Asset</t>
         </is>
       </c>
       <c r="S444" t="n">
@@ -38250,7 +38250,7 @@
       </c>
       <c r="R445" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Riza Asset</t>
         </is>
       </c>
       <c r="S445" t="n">
@@ -38335,7 +38335,7 @@
       </c>
       <c r="R446" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Riza Asset</t>
         </is>
       </c>
       <c r="S446" t="n">
@@ -38420,7 +38420,7 @@
       </c>
       <c r="R447" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Riza Asset</t>
         </is>
       </c>
       <c r="S447" t="n">
@@ -38505,7 +38505,7 @@
       </c>
       <c r="R448" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Riza Asset</t>
         </is>
       </c>
       <c r="S448" t="n">
@@ -38590,7 +38590,7 @@
       </c>
       <c r="R449" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Riza Asset</t>
         </is>
       </c>
       <c r="S449" t="n">
@@ -38675,7 +38675,7 @@
       </c>
       <c r="R450" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Riza Asset</t>
         </is>
       </c>
       <c r="S450" t="n">
@@ -38760,7 +38760,7 @@
       </c>
       <c r="R451" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Riza Asset</t>
         </is>
       </c>
       <c r="S451" t="n">
@@ -38845,7 +38845,7 @@
       </c>
       <c r="R452" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Riza Asset</t>
         </is>
       </c>
       <c r="S452" t="n">
@@ -38930,7 +38930,7 @@
       </c>
       <c r="R453" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Santander CCTVM</t>
         </is>
       </c>
       <c r="S453" t="n">
@@ -39015,7 +39015,7 @@
       </c>
       <c r="R454" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Santander CCTVM</t>
         </is>
       </c>
       <c r="S454" t="n">
@@ -39100,7 +39100,7 @@
       </c>
       <c r="R455" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Santander CCTVM</t>
         </is>
       </c>
       <c r="S455" t="n">
@@ -39185,7 +39185,7 @@
       </c>
       <c r="R456" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Santander CCTVM</t>
         </is>
       </c>
       <c r="S456" t="n">
@@ -39270,7 +39270,7 @@
       </c>
       <c r="R457" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S457" t="n">
@@ -39355,7 +39355,7 @@
       </c>
       <c r="R458" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S458" t="n">
@@ -39440,7 +39440,7 @@
       </c>
       <c r="R459" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S459" t="n">
@@ -39525,7 +39525,7 @@
       </c>
       <c r="R460" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S460" t="n">
@@ -39610,7 +39610,7 @@
       </c>
       <c r="R461" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S461" t="n">
@@ -39695,7 +39695,7 @@
       </c>
       <c r="R462" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S462" t="n">
@@ -39780,7 +39780,7 @@
       </c>
       <c r="R463" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S463" t="n">
@@ -39865,7 +39865,7 @@
       </c>
       <c r="R464" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S464" t="n">
@@ -39950,7 +39950,7 @@
       </c>
       <c r="R465" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S465" t="n">
@@ -40035,7 +40035,7 @@
       </c>
       <c r="R466" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S466" t="n">
@@ -40120,7 +40120,7 @@
       </c>
       <c r="R467" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S467" t="n">
@@ -40205,7 +40205,7 @@
       </c>
       <c r="R468" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S468" t="n">
@@ -40290,7 +40290,7 @@
       </c>
       <c r="R469" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Suno Asset</t>
         </is>
       </c>
       <c r="S469" t="n">
@@ -40375,7 +40375,7 @@
       </c>
       <c r="R470" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Suno Asset</t>
         </is>
       </c>
       <c r="S470" t="n">
@@ -40460,7 +40460,7 @@
       </c>
       <c r="R471" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Suno Asset</t>
         </is>
       </c>
       <c r="S471" t="n">
@@ -40545,7 +40545,7 @@
       </c>
       <c r="R472" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Suno Asset</t>
         </is>
       </c>
       <c r="S472" t="n">
@@ -40630,7 +40630,7 @@
       </c>
       <c r="R473" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Suno Asset</t>
         </is>
       </c>
       <c r="S473" t="n">
@@ -40715,7 +40715,7 @@
       </c>
       <c r="R474" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Suno Asset</t>
         </is>
       </c>
       <c r="S474" t="n">
@@ -40800,7 +40800,7 @@
       </c>
       <c r="R475" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Suno Asset</t>
         </is>
       </c>
       <c r="S475" t="n">
@@ -40885,7 +40885,7 @@
       </c>
       <c r="R476" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Suno Asset</t>
         </is>
       </c>
       <c r="S476" t="n">
@@ -40970,7 +40970,7 @@
       </c>
       <c r="R477" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S477" t="n">
@@ -41055,7 +41055,7 @@
       </c>
       <c r="R478" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S478" t="n">
@@ -41140,7 +41140,7 @@
       </c>
       <c r="R479" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S479" t="n">
@@ -41225,7 +41225,7 @@
       </c>
       <c r="R480" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S480" t="n">
@@ -41310,7 +41310,7 @@
       </c>
       <c r="R481" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S481" t="n">
@@ -41395,7 +41395,7 @@
       </c>
       <c r="R482" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S482" t="n">
@@ -41480,7 +41480,7 @@
       </c>
       <c r="R483" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S483" t="n">
@@ -41565,7 +41565,7 @@
       </c>
       <c r="R484" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S484" t="n">
@@ -41650,7 +41650,7 @@
       </c>
       <c r="R485" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S485" t="n">
@@ -41735,7 +41735,7 @@
       </c>
       <c r="R486" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S486" t="n">
@@ -41820,7 +41820,7 @@
       </c>
       <c r="R487" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S487" t="n">
@@ -41905,7 +41905,7 @@
       </c>
       <c r="R488" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S488" t="n">
@@ -41990,7 +41990,7 @@
       </c>
       <c r="R489" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Vortx</t>
         </is>
       </c>
       <c r="S489" t="n">
@@ -42075,7 +42075,7 @@
       </c>
       <c r="R490" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S490" t="n">
@@ -42160,7 +42160,7 @@
       </c>
       <c r="R491" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S491" t="n">
@@ -42245,7 +42245,7 @@
       </c>
       <c r="R492" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S492" t="n">
@@ -42330,7 +42330,7 @@
       </c>
       <c r="R493" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S493" t="n">
@@ -42415,7 +42415,7 @@
       </c>
       <c r="R494" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S494" t="n">
@@ -42500,7 +42500,7 @@
       </c>
       <c r="R495" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S495" t="n">
@@ -42585,7 +42585,7 @@
       </c>
       <c r="R496" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BRL Trust</t>
         </is>
       </c>
       <c r="S496" t="n">
@@ -42670,7 +42670,7 @@
       </c>
       <c r="R497" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BRL Trust</t>
         </is>
       </c>
       <c r="S497" t="n">
@@ -42755,7 +42755,7 @@
       </c>
       <c r="R498" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BRL Trust</t>
         </is>
       </c>
       <c r="S498" t="n">
@@ -42840,7 +42840,7 @@
       </c>
       <c r="R499" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BRL Trust</t>
         </is>
       </c>
       <c r="S499" t="n">
@@ -42925,7 +42925,7 @@
       </c>
       <c r="R500" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BRL Trust</t>
         </is>
       </c>
       <c r="S500" t="n">
@@ -43010,7 +43010,7 @@
       </c>
       <c r="R501" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BRL Trust</t>
         </is>
       </c>
       <c r="S501" t="n">
@@ -43095,7 +43095,7 @@
       </c>
       <c r="R502" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BRL Trust</t>
         </is>
       </c>
       <c r="S502" t="n">
@@ -43180,7 +43180,7 @@
       </c>
       <c r="R503" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S503" t="n">
@@ -43265,7 +43265,7 @@
       </c>
       <c r="R504" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S504" t="n">
@@ -43350,7 +43350,7 @@
       </c>
       <c r="R505" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S505" t="n">
@@ -43435,7 +43435,7 @@
       </c>
       <c r="R506" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Itaú DTVM</t>
         </is>
       </c>
       <c r="S506" t="n">
@@ -43520,7 +43520,7 @@
       </c>
       <c r="R507" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S507" t="n">
@@ -43605,7 +43605,7 @@
       </c>
       <c r="R508" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S508" t="n">
@@ -43690,7 +43690,7 @@
       </c>
       <c r="R509" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S509" t="n">
@@ -43775,7 +43775,7 @@
       </c>
       <c r="R510" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S510" t="n">
@@ -43860,7 +43860,7 @@
       </c>
       <c r="R511" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S511" t="n">
@@ -43945,7 +43945,7 @@
       </c>
       <c r="R512" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S512" t="n">
@@ -44030,7 +44030,7 @@
       </c>
       <c r="R513" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S513" t="n">
@@ -44115,7 +44115,7 @@
       </c>
       <c r="R514" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Banco Genial</t>
         </is>
       </c>
       <c r="S514" t="n">
@@ -44200,7 +44200,7 @@
       </c>
       <c r="R515" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Banco Genial</t>
         </is>
       </c>
       <c r="S515" t="n">
@@ -44285,7 +44285,7 @@
       </c>
       <c r="R516" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Banco Genial</t>
         </is>
       </c>
       <c r="S516" t="n">
@@ -44370,7 +44370,7 @@
       </c>
       <c r="R517" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Banco Genial</t>
         </is>
       </c>
       <c r="S517" t="n">
@@ -44455,7 +44455,7 @@
       </c>
       <c r="R518" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Banco Genial</t>
         </is>
       </c>
       <c r="S518" t="n">
@@ -44540,7 +44540,7 @@
       </c>
       <c r="R519" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Banco Genial</t>
         </is>
       </c>
       <c r="S519" t="n">
@@ -44625,7 +44625,7 @@
       </c>
       <c r="R520" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S520" t="n">
@@ -44710,7 +44710,7 @@
       </c>
       <c r="R521" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BRL Trust</t>
         </is>
       </c>
       <c r="S521" t="n">
@@ -44795,7 +44795,7 @@
       </c>
       <c r="R522" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BRL Trust</t>
         </is>
       </c>
       <c r="S522" t="n">
@@ -44880,7 +44880,7 @@
       </c>
       <c r="R523" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BRL Trust</t>
         </is>
       </c>
       <c r="S523" t="n">
@@ -44965,7 +44965,7 @@
       </c>
       <c r="R524" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BRL Trust</t>
         </is>
       </c>
       <c r="S524" t="n">
@@ -45050,7 +45050,7 @@
       </c>
       <c r="R525" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BRL Trust</t>
         </is>
       </c>
       <c r="S525" t="n">
@@ -45135,7 +45135,7 @@
       </c>
       <c r="R526" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S526" t="n">
@@ -45220,7 +45220,7 @@
       </c>
       <c r="R527" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S527" t="n">
@@ -45305,7 +45305,7 @@
       </c>
       <c r="R528" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S528" t="n">
@@ -45390,7 +45390,7 @@
       </c>
       <c r="R529" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S529" t="n">
@@ -45475,7 +45475,7 @@
       </c>
       <c r="R530" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Banco Fator</t>
         </is>
       </c>
       <c r="S530" t="n">
@@ -45560,7 +45560,7 @@
       </c>
       <c r="R531" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Banco Fator</t>
         </is>
       </c>
       <c r="S531" t="n">
@@ -45645,7 +45645,7 @@
       </c>
       <c r="R532" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S532" t="n">
@@ -45730,7 +45730,7 @@
       </c>
       <c r="R533" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S533" t="n">
@@ -45815,7 +45815,7 @@
       </c>
       <c r="R534" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S534" t="n">
@@ -45900,7 +45900,7 @@
       </c>
       <c r="R535" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S535" t="n">
@@ -45985,7 +45985,7 @@
       </c>
       <c r="R536" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S536" t="n">
@@ -46070,7 +46070,7 @@
       </c>
       <c r="R537" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S537" t="n">
@@ -46155,7 +46155,7 @@
       </c>
       <c r="R538" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S538" t="n">
@@ -46240,7 +46240,7 @@
       </c>
       <c r="R539" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S539" t="n">
@@ -46325,7 +46325,7 @@
       </c>
       <c r="R540" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S540" t="n">
@@ -46410,7 +46410,7 @@
       </c>
       <c r="R541" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S541" t="n">
@@ -46495,7 +46495,7 @@
       </c>
       <c r="R542" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S542" t="n">
@@ -46580,7 +46580,7 @@
       </c>
       <c r="R543" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S543" t="n">
@@ -46665,7 +46665,7 @@
       </c>
       <c r="R544" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S544" t="n">
@@ -46750,7 +46750,7 @@
       </c>
       <c r="R545" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S545" t="n">
@@ -46835,7 +46835,7 @@
       </c>
       <c r="R546" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S546" t="n">
@@ -46920,7 +46920,7 @@
       </c>
       <c r="R547" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>XP Investimentos</t>
         </is>
       </c>
       <c r="S547" t="n">
@@ -47005,7 +47005,7 @@
       </c>
       <c r="R548" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>XP Investimentos</t>
         </is>
       </c>
       <c r="S548" t="n">
@@ -47090,7 +47090,7 @@
       </c>
       <c r="R549" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>XP Investimentos</t>
         </is>
       </c>
       <c r="S549" t="n">
@@ -47175,7 +47175,7 @@
       </c>
       <c r="R550" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>XP Investimentos</t>
         </is>
       </c>
       <c r="S550" t="n">
@@ -47260,7 +47260,7 @@
       </c>
       <c r="R551" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>XP Investimentos</t>
         </is>
       </c>
       <c r="S551" t="n">
@@ -47345,7 +47345,7 @@
       </c>
       <c r="R552" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>XP Investimentos</t>
         </is>
       </c>
       <c r="S552" t="n">
@@ -47430,7 +47430,7 @@
       </c>
       <c r="R553" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>XP Investimentos</t>
         </is>
       </c>
       <c r="S553" t="n">
@@ -47515,7 +47515,7 @@
       </c>
       <c r="R554" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>XP Investimentos</t>
         </is>
       </c>
       <c r="S554" t="n">
@@ -47600,7 +47600,7 @@
       </c>
       <c r="R555" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>XP Investimentos</t>
         </is>
       </c>
       <c r="S555" t="n">
@@ -47685,7 +47685,7 @@
       </c>
       <c r="R556" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S556" t="n">
@@ -47770,7 +47770,7 @@
       </c>
       <c r="R557" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S557" t="n">
@@ -47855,7 +47855,7 @@
       </c>
       <c r="R558" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S558" t="n">
@@ -47940,7 +47940,7 @@
       </c>
       <c r="R559" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S559" t="n">
@@ -48025,7 +48025,7 @@
       </c>
       <c r="R560" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S560" t="n">
@@ -48110,7 +48110,7 @@
       </c>
       <c r="R561" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S561" t="n">
@@ -48195,7 +48195,7 @@
       </c>
       <c r="R562" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>BTG Pactual / Outros</t>
         </is>
       </c>
       <c r="S562" t="n">

--- a/fiis_b3.xlsx
+++ b/fiis_b3.xlsx
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -7459,7 +7459,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -10889,7 +10889,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -12751,7 +12751,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -13927,7 +13927,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
@@ -14711,7 +14711,7 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
@@ -14907,7 +14907,7 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
@@ -15005,7 +15005,7 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
@@ -15201,7 +15201,7 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
@@ -15691,7 +15691,7 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
@@ -15887,7 +15887,7 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
@@ -15985,7 +15985,7 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
@@ -16377,7 +16377,7 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
@@ -16671,7 +16671,7 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         </is>
       </c>
       <c r="P178" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Q178" t="inlineStr">
         <is>
@@ -18533,7 +18533,7 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
@@ -19219,7 +19219,7 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
@@ -19709,7 +19709,7 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q197" t="inlineStr">
         <is>
@@ -19807,7 +19807,7 @@
         </is>
       </c>
       <c r="P198" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q198" t="inlineStr">
         <is>
@@ -20003,7 +20003,7 @@
         </is>
       </c>
       <c r="P200" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q200" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         </is>
       </c>
       <c r="P203" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q203" t="inlineStr">
         <is>
@@ -20395,7 +20395,7 @@
         </is>
       </c>
       <c r="P204" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q204" t="inlineStr">
         <is>
@@ -20493,7 +20493,7 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q205" t="inlineStr">
         <is>
@@ -20787,7 +20787,7 @@
         </is>
       </c>
       <c r="P208" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q208" t="inlineStr">
         <is>
@@ -20885,7 +20885,7 @@
         </is>
       </c>
       <c r="P209" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q209" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         </is>
       </c>
       <c r="P210" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q210" t="inlineStr">
         <is>
@@ -21081,7 +21081,7 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q211" t="inlineStr">
         <is>
@@ -21473,7 +21473,7 @@
         </is>
       </c>
       <c r="P215" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q215" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         </is>
       </c>
       <c r="P218" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q218" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         </is>
       </c>
       <c r="P219" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q219" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         </is>
       </c>
       <c r="P220" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q220" t="inlineStr">
         <is>
@@ -22453,7 +22453,7 @@
         </is>
       </c>
       <c r="P225" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q225" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         </is>
       </c>
       <c r="P227" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q227" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         </is>
       </c>
       <c r="P229" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q229" t="inlineStr">
         <is>
@@ -24315,7 +24315,7 @@
         </is>
       </c>
       <c r="P244" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q244" t="inlineStr">
         <is>
@@ -24413,7 +24413,7 @@
         </is>
       </c>
       <c r="P245" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q245" t="inlineStr">
         <is>
@@ -25687,7 +25687,7 @@
         </is>
       </c>
       <c r="P258" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q258" t="inlineStr">
         <is>
@@ -26177,7 +26177,7 @@
         </is>
       </c>
       <c r="P263" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q263" t="inlineStr">
         <is>
@@ -26667,7 +26667,7 @@
         </is>
       </c>
       <c r="P268" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q268" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         </is>
       </c>
       <c r="P273" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q273" t="inlineStr">
         <is>
@@ -27353,7 +27353,7 @@
         </is>
       </c>
       <c r="P275" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q275" t="inlineStr">
         <is>
@@ -27451,7 +27451,7 @@
         </is>
       </c>
       <c r="P276" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Q276" t="inlineStr">
         <is>
@@ -27647,7 +27647,7 @@
         </is>
       </c>
       <c r="P278" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Q278" t="inlineStr">
         <is>
@@ -27745,7 +27745,7 @@
         </is>
       </c>
       <c r="P279" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q279" t="inlineStr">
         <is>
@@ -29999,7 +29999,7 @@
         </is>
       </c>
       <c r="P302" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q302" t="inlineStr">
         <is>
@@ -30391,7 +30391,7 @@
         </is>
       </c>
       <c r="P306" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q306" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         </is>
       </c>
       <c r="P307" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q307" t="inlineStr">
         <is>
@@ -30587,7 +30587,7 @@
         </is>
       </c>
       <c r="P308" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q308" t="inlineStr">
         <is>
@@ -31371,7 +31371,7 @@
         </is>
       </c>
       <c r="P316" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q316" t="inlineStr">
         <is>
@@ -32449,7 +32449,7 @@
         </is>
       </c>
       <c r="P327" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q327" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         </is>
       </c>
       <c r="P330" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q330" t="inlineStr">
         <is>
@@ -33037,7 +33037,7 @@
         </is>
       </c>
       <c r="P333" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q333" t="inlineStr">
         <is>
@@ -33135,7 +33135,7 @@
         </is>
       </c>
       <c r="P334" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q334" t="inlineStr">
         <is>
@@ -33429,7 +33429,7 @@
         </is>
       </c>
       <c r="P337" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q337" t="inlineStr">
         <is>
@@ -33527,7 +33527,7 @@
         </is>
       </c>
       <c r="P338" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q338" t="inlineStr">
         <is>
@@ -34605,7 +34605,7 @@
         </is>
       </c>
       <c r="P349" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Q349" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         </is>
       </c>
       <c r="P354" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q354" t="inlineStr">
         <is>
@@ -35291,7 +35291,7 @@
         </is>
       </c>
       <c r="P356" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q356" t="inlineStr">
         <is>
@@ -35683,7 +35683,7 @@
         </is>
       </c>
       <c r="P360" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q360" t="inlineStr">
         <is>
@@ -36075,7 +36075,7 @@
         </is>
       </c>
       <c r="P364" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q364" t="inlineStr">
         <is>
@@ -36369,7 +36369,7 @@
         </is>
       </c>
       <c r="P367" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q367" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         </is>
       </c>
       <c r="P373" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q373" t="inlineStr">
         <is>
@@ -37153,7 +37153,7 @@
         </is>
       </c>
       <c r="P375" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q375" t="inlineStr">
         <is>
@@ -37251,7 +37251,7 @@
         </is>
       </c>
       <c r="P376" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q376" t="inlineStr">
         <is>
@@ -37349,7 +37349,7 @@
         </is>
       </c>
       <c r="P377" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q377" t="inlineStr">
         <is>
@@ -37447,7 +37447,7 @@
         </is>
       </c>
       <c r="P378" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q378" t="inlineStr">
         <is>
@@ -38427,7 +38427,7 @@
         </is>
       </c>
       <c r="P388" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q388" t="inlineStr">
         <is>
@@ -38525,7 +38525,7 @@
         </is>
       </c>
       <c r="P389" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q389" t="inlineStr">
         <is>
@@ -38819,7 +38819,7 @@
         </is>
       </c>
       <c r="P392" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q392" t="inlineStr">
         <is>
@@ -39309,7 +39309,7 @@
         </is>
       </c>
       <c r="P397" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q397" t="inlineStr">
         <is>
@@ -39603,7 +39603,7 @@
         </is>
       </c>
       <c r="P400" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q400" t="inlineStr">
         <is>
@@ -39701,7 +39701,7 @@
         </is>
       </c>
       <c r="P401" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q401" t="inlineStr">
         <is>
@@ -39799,7 +39799,7 @@
         </is>
       </c>
       <c r="P402" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Q402" t="inlineStr">
         <is>
@@ -40093,7 +40093,7 @@
         </is>
       </c>
       <c r="P405" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q405" t="inlineStr">
         <is>
@@ -40191,7 +40191,7 @@
         </is>
       </c>
       <c r="P406" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q406" t="inlineStr">
         <is>
@@ -40289,7 +40289,7 @@
         </is>
       </c>
       <c r="P407" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q407" t="inlineStr">
         <is>
@@ -40583,7 +40583,7 @@
         </is>
       </c>
       <c r="P410" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q410" t="inlineStr">
         <is>
@@ -40681,7 +40681,7 @@
         </is>
       </c>
       <c r="P411" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q411" t="inlineStr">
         <is>
@@ -40779,7 +40779,7 @@
         </is>
       </c>
       <c r="P412" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q412" t="inlineStr">
         <is>
@@ -41073,7 +41073,7 @@
         </is>
       </c>
       <c r="P415" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q415" t="inlineStr">
         <is>
@@ -41955,7 +41955,7 @@
         </is>
       </c>
       <c r="P424" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q424" t="inlineStr">
         <is>
@@ -42151,7 +42151,7 @@
         </is>
       </c>
       <c r="P426" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q426" t="inlineStr">
         <is>
@@ -42543,7 +42543,7 @@
         </is>
       </c>
       <c r="P430" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q430" t="inlineStr">
         <is>
@@ -42935,7 +42935,7 @@
         </is>
       </c>
       <c r="P434" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q434" t="inlineStr">
         <is>
@@ -43033,7 +43033,7 @@
         </is>
       </c>
       <c r="P435" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q435" t="inlineStr">
         <is>
@@ -43523,7 +43523,7 @@
         </is>
       </c>
       <c r="P440" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q440" t="inlineStr">
         <is>
@@ -44895,7 +44895,7 @@
         </is>
       </c>
       <c r="P454" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q454" t="inlineStr">
         <is>
@@ -45091,7 +45091,7 @@
         </is>
       </c>
       <c r="P456" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q456" t="inlineStr">
         <is>
@@ -45189,7 +45189,7 @@
         </is>
       </c>
       <c r="P457" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q457" t="inlineStr">
         <is>
@@ -45287,7 +45287,7 @@
         </is>
       </c>
       <c r="P458" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q458" t="inlineStr">
         <is>
@@ -45875,7 +45875,7 @@
         </is>
       </c>
       <c r="P464" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q464" t="inlineStr">
         <is>
@@ -47639,7 +47639,7 @@
         </is>
       </c>
       <c r="P482" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q482" t="inlineStr">
         <is>
@@ -48227,7 +48227,7 @@
         </is>
       </c>
       <c r="P488" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q488" t="inlineStr">
         <is>
@@ -48325,7 +48325,7 @@
         </is>
       </c>
       <c r="P489" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Q489" t="inlineStr">
         <is>
@@ -49207,7 +49207,7 @@
         </is>
       </c>
       <c r="P498" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q498" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         </is>
       </c>
       <c r="P500" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q500" t="inlineStr">
         <is>
@@ -50285,7 +50285,7 @@
         </is>
       </c>
       <c r="P509" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q509" t="inlineStr">
         <is>
@@ -50677,7 +50677,7 @@
         </is>
       </c>
       <c r="P513" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q513" t="inlineStr">
         <is>
@@ -51069,7 +51069,7 @@
         </is>
       </c>
       <c r="P517" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q517" t="inlineStr">
         <is>
@@ -51167,7 +51167,7 @@
         </is>
       </c>
       <c r="P518" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q518" t="inlineStr">
         <is>
@@ -51559,7 +51559,7 @@
         </is>
       </c>
       <c r="P522" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q522" t="inlineStr">
         <is>
@@ -51657,7 +51657,7 @@
         </is>
       </c>
       <c r="P523" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q523" t="inlineStr">
         <is>
@@ -51755,7 +51755,7 @@
         </is>
       </c>
       <c r="P524" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Q524" t="inlineStr">
         <is>
@@ -52147,7 +52147,7 @@
         </is>
       </c>
       <c r="P528" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q528" t="inlineStr">
         <is>
@@ -52343,7 +52343,7 @@
         </is>
       </c>
       <c r="P530" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q530" t="inlineStr">
         <is>
@@ -52637,7 +52637,7 @@
         </is>
       </c>
       <c r="P533" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q533" t="inlineStr">
         <is>
@@ -53029,7 +53029,7 @@
         </is>
       </c>
       <c r="P537" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q537" t="inlineStr">
         <is>
@@ -53617,7 +53617,7 @@
         </is>
       </c>
       <c r="P543" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q543" t="inlineStr">
         <is>
@@ -53813,7 +53813,7 @@
         </is>
       </c>
       <c r="P545" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q545" t="inlineStr">
         <is>
@@ -54107,7 +54107,7 @@
         </is>
       </c>
       <c r="P548" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q548" t="inlineStr">
         <is>
@@ -54205,7 +54205,7 @@
         </is>
       </c>
       <c r="P549" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q549" t="inlineStr">
         <is>
@@ -54303,7 +54303,7 @@
         </is>
       </c>
       <c r="P550" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q550" t="inlineStr">
         <is>
@@ -54401,7 +54401,7 @@
         </is>
       </c>
       <c r="P551" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q551" t="inlineStr">
         <is>
@@ -54499,7 +54499,7 @@
         </is>
       </c>
       <c r="P552" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q552" t="inlineStr">
         <is>
@@ -54597,7 +54597,7 @@
         </is>
       </c>
       <c r="P553" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q553" t="inlineStr">
         <is>
@@ -54793,7 +54793,7 @@
         </is>
       </c>
       <c r="P555" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q555" t="inlineStr">
         <is>
